--- a/scripts/rf_standard_l2/performance.xlsx
+++ b/scripts/rf_standard_l2/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="490">
   <si>
     <t>Model</t>
   </si>
@@ -236,7 +241,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.0004602636409738648), np.float64(4.372619057622731e-41)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008279556785965497), np.float64(0.6798094317123905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.065653770196407), np.float64(0.2868950036078551)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0029873499281967723), np.float64(0.05561044903477068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0034902744060696456), np.float64(0.09343235750689077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0012869511105851163), np.float64(0.27086586785045474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0011558194185039164), np.float64(0.6208248392703706)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003746833325948795), np.float64(6.556086762215437e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007677398470197491), np.float64(4.5306302950251456e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.019048956055949792), np.float64(5.0065882546396995e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03755611166303689), np.float64(6.436412104538137e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09327484315641343), np.float64(9.192032351100215e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.18209203696081838), np.float64(3.8927394286508e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00030693485175911265), np.float64(0.452153707150602)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00022087885984712282), np.float64(0.677559243588973)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008387168650053593), np.float64(0.18248076287575188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0027519245016146584), np.float64(0.02840352090604832)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006072370867736206), np.float64(0.01548768152941617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012214710985808928), np.float64(0.014448812138219412)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.030306716717035862), np.float64(0.015609776858433849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.059697107355341006), np.float64(0.015080527058769154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.14944575403825983), np.float64(0.017082791600316435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2830121087640403), np.float64(0.012947428870312246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003821638483372952), np.float64(0.0005846017763355628)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-8.659439593388138e-05), np.float64(0.5502030256487023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00016791051507834248), np.float64(0.34529620250825677)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011138141164312044), np.float64(0.000979341775076163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0024844523315092244), np.float64(0.00022349079520234214)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0052172512293921485), np.float64(8.811822988018868e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01262253272981637), np.float64(0.00013930511957569445)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.024871269203841), np.float64(0.00022106551888654294)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06042595976448564), np.float64(0.0002442953859904717)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1268265906236246), np.float64(0.0004020950241410951)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00011745516175458997), np.float64(0.306301404435939)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00011703198076379532), np.float64(0.4350078377063398)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003065383461006159), np.float64(0.10036162939035506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00099599720434458), np.float64(0.007203693903441574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002185692159494269), np.float64(0.0028398066289688157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004241565250387536), np.float64(0.0037354692327094406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010034536630520882), np.float64(0.006044354068009277)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01963379712725281), np.float64(0.007244476643827507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04703130474018709), np.float64(0.008326585333340323)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09756192760718653), np.float64(0.013047839353734242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.866699381937262e-05), np.float64(0.21146437971358978)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0167509026036228e-05), np.float64(0.674150605539003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001211205406915875), np.float64(0.15327500441840053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004858005594870373), np.float64(1.5096239051201993e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008576476955942519), np.float64(8.163335831017502e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014326529229799424), np.float64(0.0008382627087697467)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002873176447515396), np.float64(0.006773362620777992)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005199104176679228), np.float64(0.01422093782209891)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01217736160148375), np.float64(0.025901435689814418)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02384678878958264), np.float64(0.03057464756136508)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00023603512258575272), np.float64(4.163393818814771e-20)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00028694824374052833), np.float64(1.6707024517316038e-25)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00032839445796960015), np.float64(5.1792379731724784e-30)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004598600195579511), np.float64(6.057778721249714e-41)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005970843975231741), np.float64(1.8691003242610862e-44)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007438749437538204), np.float64(1.3207813467531174e-39)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009050479999607286), np.float64(1.0468326616478498e-24)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010434917948915297), np.float64(3.1863826663820057e-16)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011286820045212905), np.float64(4.3092833146867635e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0012083184277947663), np.float64(6.350053127523879e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.22801505897548838), np.float64(0.01892239643913544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.31832041139616374), np.float64(0.01385132525221434)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2134433699785939), np.float64(0.0033598939563576715)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4191986223497253), np.float64(0.003914206393300848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0592309833014566), np.float64(0.3009296198359738)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08670542325214065), np.float64(0.4512151031259768)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2854218567639904), np.float64(0.3138946135357772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.696117519847958), np.float64(0.21513008762837385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1017313491187304), np.float64(0.13483913462724187)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.698971205570371), np.float64(0.14739639801817245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006883252248655748), np.float64(0.7866994069021603)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00892419539258699), np.float64(0.7869628212798456)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006524331947025955), np.float64(0.8673366389735305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01596118136961325), np.float64(0.8375522996235407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.031213731025725763), np.float64(0.8389963711666314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04454841597244307), np.float64(0.8839116311565601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1286883738674922), np.float64(0.8653836081009046)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06898125942420237), np.float64(0.9626595895298308)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8534945411371334), np.float64(0.8170311197927621)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.3147569845514897), np.float64(0.6153194491499343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.58718096003195e-05), np.float64(0.9900612082756983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007638645865060548), np.float64(0.9324783090126076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0036183123585119105), np.float64(0.7435808406527531)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009473040772760422), np.float64(0.6502761841798709)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.019456965737712315), np.float64(0.6359626078000938)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.027007741846495268), np.float64(0.7377055381551406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07094647038696617), np.float64(0.7226690858392645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.19775637143241842), np.float64(0.6223518950817695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5823492515066775), np.float64(0.5455673985315534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0035824423605059254), np.float64(0.9986227771473043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0035598171274766107), np.float64(0.6186762857036692)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.005256098402354305), np.float64(0.5736557101561002)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006319372551770067), np.float64(0.5869865911710308)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.010862089161211714), np.float64(0.6359132381561704)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.035679683261769825), np.float64(0.4270962139503197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0681851570807642), np.float64(0.44238851646809196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.17188041395351092), np.float64(0.4355721186419698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.38744237295247513), np.float64(0.37567421166536874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6738846759323118), np.float64(0.520190086200727)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.151784234045884), np.float64(0.6131214055016638)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007747567240272715), np.float64(0.02388210241516341)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010572202796872135), np.float64(0.01842473177570437)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009934210043005808), np.float64(0.06037757861598647)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008975486591495902), np.float64(0.1956140187063271)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.021681680966648208), np.float64(0.10411450429420696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03978393898018804), np.float64(0.1274338820450545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09241045986529534), np.float64(0.14815994950531003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.16643269151811965), np.float64(0.18777061630845815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2812179526802487), np.float64(0.3845369556484928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5271722790786844), np.float64(0.408365487976867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(9.831612792596017e-05), np.float64(0.9495331136561348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.438598876728493e-05), np.float64(0.9688237109146783)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.038470115733835e-05), np.float64(0.9626698241256958)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008043618211829869), np.float64(0.688752796162022)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0015766385045864544), np.float64(0.5232727622792196)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004197841981488609), np.float64(0.20137126961037066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007269374643114659), np.float64(0.16065268986129505)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.012671653233505983), np.float64(0.09505807619543902)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01377485936813642), np.float64(0.2555328285281572)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.011986780836894747), np.float64(0.43274702674274496)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.3746767347203575), np.float64(0.017794364887433772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.018400546294786), np.float64(0.04387588037155173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7317283867051572), np.float64(0.08369939895296466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.75458597445981), np.float64(0.45071488703803125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.6071010530428858), np.float64(0.00929775176668837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5505915496390132), np.float64(0.0004063465706404118)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.943807797233476), np.float64(8.707994571356243e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.9942553906986444), np.float64(7.075124829349395e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.9845628806001483), np.float64(7.364410805259635e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.207657498476157), np.float64(2.866156666545585e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.028079911516022), np.float64(0.042876108361283506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.163261506976286), np.float64(0.24506305028017644)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.29796306028277536), np.float64(0.7658071123601363)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2646873425509089), np.float64(0.206344062150015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9964973655711569), np.float64(0.046211230761358704)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.273299812647658), np.float64(0.023266920510748423)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3659858058126093), np.float64(0.018214638396666025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4033310978507942), np.float64(0.016468402441419363)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3930058325661534), np.float64(0.01693582483995375)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5200606415612334), np.float64(0.011923007581493618)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.6323737124143394), np.float64(0.008639114348005779)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.095699992767582), np.float64(0.03641600964884849)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5647345162648385), np.float64(0.118032401480892)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.13921830268265822), np.float64(0.8893119554467137)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7391496466171437), np.float64(0.08238509027324127)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0291757581699077), np.float64(0.0025294294901303683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5353402542707584), np.float64(0.00043015955872638254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5946592340147467), np.float64(0.00034428847901354394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6675015841788783), np.float64(0.0002607903854818645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5323673398101554), np.float64(0.0004349508462026648)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.165141012261064), np.float64(0.030665716570817222)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7334489381648903), np.float64(0.083393183729363)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2713843422379805), np.float64(0.2039537762619292)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.09246396957991024), np.float64(0.9263520841979871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2244997838376799), np.float64(0.22111670255279303)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0322825490137597), np.float64(0.0424480672022741)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4061051195595002), np.float64(0.016344773977529856)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4881387345925976), np.float64(0.013039627684949017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5574987899851997), np.float64(0.010722286224809889)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4310233224898576), np.float64(0.015270384868161452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1030222184495044), np.float64(0.03576913415623819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8899252087902343), np.float64(0.059121723772588876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6282168693386774), np.float64(0.10386443861720013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9460819878024351), np.float64(0.3443864892736106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2721551182250357), np.float64(0.7855715127542611)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6175065635046694), np.float64(0.537072720691887)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6401697482504447), np.float64(0.10135480498522446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9818390248104474), np.float64(0.047832003590809184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.098646148240339), np.float64(0.036154543110977384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1246143633694903), np.float64(0.03391846870426604)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4759776991399192), np.float64(0.14033517254280178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3565051710170235), np.float64(0.17531321026382637)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2577366061330524), np.float64(0.20884639724723045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0684433967440714), np.float64(0.2856361341206317)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7560917900396739), np.float64(0.4498121108620324)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5960519728277117), np.float64(0.5513056015174265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4963609997917801), np.float64(0.6197732485848517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3036574135577724), np.float64(0.7614662189491468)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007862657984525354), np.float64(0.9937284906648067)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10852676970583136), np.float64(0.9136044942040326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0032486367221332786), np.float64(0.054185710443431075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0038694401940407696), np.float64(0.08546877244997883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001717799679353656), np.float64(0.21918262523660148)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0028204850439185226), np.float64(0.44483506949096313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00358374586120735), np.float64(1.5408559887774075e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0073217408457689195), np.float64(3.3967638306150155e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.018884052691822455), np.float64(4.359377582564967e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.036543192875024895), np.float64(1.6813718457258215e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0918219951778101), np.float64(4.040335553286552e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1780432445769641), np.float64(1.739007597209431e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003365027215630465), np.float64(0.40107484689040257)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00013975595315430262), np.float64(0.7718267047345008)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007634220149743591), np.float64(0.19544238379336518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00243672542459593), np.float64(0.013309771612644083)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0049804958134317), np.float64(0.0005565662335066156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009770935835248105), np.float64(0.00044205815919594305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.023990875996546757), np.float64(0.0005229101842306946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0493005879143792), np.float64(0.001330450064728378)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12298235705282681), np.float64(0.001494147091151755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.23446021049867802), np.float64(0.0007255542356866115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003993226167745034), np.float64(0.0002959610375621235)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00011327334930620372), np.float64(0.4297507901713926)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00010795210902972981), np.float64(0.5458728665396264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010703065568226405), np.float64(0.0011587421230631818)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0023867911844786763), np.float64(0.0002207830023471301)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004976141964427177), np.float64(4.2380475677130224e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.011954806912397418), np.float64(4.705620397747334e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02379702708006005), np.float64(0.00011049849704317325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.058855209658260216), np.float64(0.00020623257540903914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12379255389990912), np.float64(0.0003184086226907197)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00012735986948047336), np.float64(0.2611589045619147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00010511357990259244), np.float64(0.477488230119986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00029724005098422714), np.float64(0.10833268547757853)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009408071649319238), np.float64(0.007340768219029578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0020817887576639227), np.float64(0.002929796007441091)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003960485369032472), np.float64(0.0028589131772151534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00918675173634802), np.float64(0.003116576380208337)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017840533940435124), np.float64(0.003544257372836234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.043806903494154815), np.float64(0.004542702036635013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09211673602382926), np.float64(0.009412972417391058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00017729168830422502), np.float64(0.14100179175395755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00011660046834257281), np.float64(0.4959958945634543)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.055036543287884e-05), np.float64(0.7378884568163068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(8.375492364503491e-05), np.float64(0.837384298206953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00011609759264423143), np.float64(0.8781651258946217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002547577465363445), np.float64(0.8346431437437349)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00039141412869372487), np.float64(0.9074584789261206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0020667176655835367), np.float64(0.7841051026424029)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006177746213186261), np.float64(0.748506653536417)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009395370504485395), np.float64(0.7932298008276111)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00022534889037473653), np.float64(1.0565776782562828e-18)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002776822963952054), np.float64(2.01756198809691e-24)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00031860086001106984), np.float64(6.656717935500706e-29)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00045726480199587393), np.float64(5.012190027906112e-41)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005889204697098903), np.float64(5.251685735588287e-44)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007350989893233554), np.float64(3.3200948773049864e-39)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000894528119185958), np.float64(3.1133149860813493e-24)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010375980985980356), np.float64(4.038612909923313e-16)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001128128603186996), np.float64(4.3744147408222746e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011953684847619127), np.float64(7.271077038703364e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2502576732966277), np.float64(0.01730581860095674)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.36152267780959424), np.float64(0.009720444334474287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.24542357347167268), np.float64(0.004826246537166141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6486397842968223), np.float64(0.004719881452619698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04424669819134212), np.float64(0.38104640071663975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.050745596572898996), np.float64(0.5980806617470744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2622178827260591), np.float64(0.34615457507467207)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5572889157883135), np.float64(0.2704092436719848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6891285286536593), np.float64(0.200085747324047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.344424004613534), np.float64(0.15669517864562374)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005411063681634491), np.float64(0.8282350327528615)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005347947909543134), np.float64(0.8583517052597909)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003287535372929271), np.float64(0.9285436053349194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002590840507788407), np.float64(0.9661315514757292)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.013407518377187294), np.float64(0.8790408031967433)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04372996402090273), np.float64(0.7965530880053867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.07391258121047997), np.float64(0.8596902354721851)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.21532157474439417), np.float64(0.814962877809518)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018591429039384352), np.float64(0.9993498865372202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8112327709878278), np.float64(0.8392842233690584)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00010255045696849755), np.float64(0.9880447313591454)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00019761986158801405), np.float64(0.982321049028399)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002326190065031749), np.float64(0.834210553168893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008833601187328264), np.float64(0.6645446981693287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017178237080723798), np.float64(0.6632781039496907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.025647743143669865), np.float64(0.7280645121452399)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06385555939059287), np.float64(0.7188059307426988)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.17702055716273293), np.float64(0.6297454081698765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5078632101414878), np.float64(0.5851486752804266)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.027480835858631616), np.float64(0.9889604482872288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003617570208012705), np.float64(0.6083327527209265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004878995104176104), np.float64(0.5960369472386666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00566444933715756), np.float64(0.6233434273047065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008766674428282517), np.float64(0.685950130316191)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03156321679119871), np.float64(0.4614719853945106)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.06047356303371805), np.float64(0.45327641679416136)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.1528672112860867), np.float64(0.4144185062497221)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.34249728020376047), np.float64(0.3477075641741341)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6766915279413867), np.float64(0.45383099250957526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.19930961453853), np.float64(0.5604263962409963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00375238300287824), np.float64(0.6167007181511729)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005005619738770929), np.float64(0.6393901471807502)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005082164563652073), np.float64(0.69882946825212)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00040171829474870143), np.float64(0.9873107383646057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005967465744686561), np.float64(0.8975505538576506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007038794911354213), np.float64(0.9245716388095666)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01697176672827577), np.float64(0.9333496018690899)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01777353608106206), np.float64(0.968616373264883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2346251847562101), np.float64(0.837156139817736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3686871963033961), np.float64(0.8592100684647564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002861006141511227), np.float64(0.8531648388224015)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00029562929250070307), np.float64(0.8566185663122504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00032503065598878117), np.float64(0.8485893741806771)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007512031462457418), np.float64(0.7063893595366282)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0014897685121085579), np.float64(0.5437588061259424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0038902877044682494), np.float64(0.2326103757852141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007485722790896445), np.float64(0.14791428967094045)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.013337753409388786), np.float64(0.07782199997354022)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01703297585710445), np.float64(0.15648364813127905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.011155107275185679), np.float64(0.46126908897609026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.3476362204314247), np.float64(0.019130678073467182)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0186287956825946), np.float64(0.043852079638018494)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.742932145657108), np.float64(0.08172168547821038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8651143900675681), np.float64(0.38722995295558427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.65547895309484), np.float64(0.0080738555732397)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.943681131670355), np.float64(8.71251103089279e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.9672221451640834), np.float64(7.910135670309789e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.287953028248561), np.float64(2.0186717950134263e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.166695998532216), np.float64(3.419770149566694e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.383350507500046), np.float64(1.321154532144033e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0861101288105903), np.float64(0.03727830246725218)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3312760755902422), np.float64(0.18346953397094168)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4185027833270346), np.float64(0.6756895382863298)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2341137184266748), np.float64(0.2175154035695772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5759293776822214), np.float64(0.01017172871411512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.139003147700358), np.float64(0.0017561521776177436)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.342704485355686), np.float64(0.0008673962169558944)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.147427579664121), np.float64(0.0017069204580307143)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.1679819239506304), np.float64(0.0015920910223819163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.3990692428781197), np.float64(0.0007089140359723554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.6561736283981046), np.float64(0.008057386585796916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1513232468143464), np.float64(0.03174325061276034)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6810900277590313), np.float64(0.09312763562017559)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05869794864887821), np.float64(0.9532070468303495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.647940961618849), np.float64(0.09974927578499822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0509688538834245), np.float64(0.0023547926685624364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7407245826528985), np.float64(0.00019631149328985177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7497698809908577), np.float64(0.00018948014644904685)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7047006751631213), np.float64(0.00022588634389604506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5909577653215146), np.float64(0.0003491379777915493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.193000594138097), np.float64(0.028588559295675133)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7681039042468374), np.float64(0.07741669533928217)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.326369421664481), np.float64(0.1850880083002573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.17578136353336504), np.float64(0.8605092695367157)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.13552128216795), np.float64(0.25648996928060036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0236280786016705), np.float64(0.04333351173626403)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5460470934041433), np.float64(0.011077595855976164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.681454907404346), np.float64(0.0074781609990977795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.7420863901460657), np.float64(0.006238553467035826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.541980950847176), np.float64(0.011206253830025993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.2693417678642787), np.float64(0.023507469602061754)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.105380179669492), np.float64(0.03556292322368877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8914826455046108), np.float64(0.05891341221321242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4013533243492833), np.float64(0.16148818895697858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9931604946227173), np.float64(0.3209257946947542)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5877080561157505), np.float64(0.5568906645624623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4289106041733452), np.float64(0.6681013505292842)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4284950429574212), np.float64(0.6684036860490881)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.38774712580629317), np.float64(0.6983041755439179)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.305576244558306), np.float64(0.7600051493043484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4902956090669157), np.float64(0.13653247573812458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3793166667150445), np.float64(0.16817457259150406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.293652318038418), np.float64(0.19615115202388578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.058891647842677), np.float64(0.2899620874171438)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7811353576184847), np.float64(0.43494917004001926)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.593035995924832), np.float64(0.5533211812507542)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4830577378894471), np.float64(0.6291841573533458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3759311300442711), np.float64(0.7070656883754127)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0543582309077645), np.float64(0.956663045656175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3087369053283534), np.float64(0.7576003756366001)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1695,10 +2981,6169 @@
         <v>62</v>
       </c>
       <c r="V12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W12" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.001126715862545256</v>
+      </c>
+      <c r="D2">
+        <v>-0.002738234121352434</v>
+      </c>
+      <c r="E2">
+        <v>0.04459416121244431</v>
+      </c>
+      <c r="F2">
+        <v>0.0007362175383605063</v>
+      </c>
+      <c r="G2">
+        <v>0.0007916103349998593</v>
+      </c>
+      <c r="H2">
+        <v>1.000584229301976</v>
+      </c>
+      <c r="I2">
+        <v>0.04892716915750224</v>
+      </c>
+      <c r="J2">
+        <v>-0.06140342354774475</v>
+      </c>
+      <c r="K2">
+        <v>-0.999874472618103</v>
+      </c>
+      <c r="L2">
+        <v>2.552407026290894</v>
+      </c>
+      <c r="M2">
+        <v>-3.514508008956909</v>
+      </c>
+      <c r="N2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.001499334948325776</v>
+      </c>
+      <c r="D3">
+        <v>-0.00313425250351429</v>
+      </c>
+      <c r="E3">
+        <v>0.05947659909725189</v>
+      </c>
+      <c r="F3">
+        <v>0.0008320764754898846</v>
+      </c>
+      <c r="G3">
+        <v>0.0008208841900341213</v>
+      </c>
+      <c r="H3">
+        <v>1.000855893707727</v>
+      </c>
+      <c r="I3">
+        <v>0.04883103711778158</v>
+      </c>
+      <c r="J3">
+        <v>-0.05269723758101463</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999658465385437</v>
+      </c>
+      <c r="L3">
+        <v>3.404223442077637</v>
+      </c>
+      <c r="M3">
+        <v>-3.016197681427002</v>
+      </c>
+      <c r="N3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.001871601657049427</v>
+      </c>
+      <c r="D4">
+        <v>-0.001050853985361755</v>
+      </c>
+      <c r="E4">
+        <v>0.03348307684063911</v>
+      </c>
+      <c r="F4">
+        <v>0.0009087602375075221</v>
+      </c>
+      <c r="G4">
+        <v>0.0008850334561429918</v>
+      </c>
+      <c r="H4">
+        <v>1.000995613014632</v>
+      </c>
+      <c r="I4">
+        <v>0.04881904123694114</v>
+      </c>
+      <c r="J4">
+        <v>-0.03138463199138641</v>
+      </c>
+      <c r="K4">
+        <v>-0.968073844909668</v>
+      </c>
+      <c r="L4">
+        <v>1.916449189186096</v>
+      </c>
+      <c r="M4">
+        <v>-1.796341776847839</v>
+      </c>
+      <c r="N4" t="s">
+        <v>131</v>
+      </c>
+      <c r="O4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.003724331478269532</v>
+      </c>
+      <c r="D5">
+        <v>-0.0007091363659128547</v>
+      </c>
+      <c r="E5">
+        <v>0.06695370376110077</v>
+      </c>
+      <c r="F5">
+        <v>0.001287848805077374</v>
+      </c>
+      <c r="G5">
+        <v>0.001226168940775096</v>
+      </c>
+      <c r="H5">
+        <v>1.001081929395629</v>
+      </c>
+      <c r="I5">
+        <v>0.04891388238933191</v>
+      </c>
+      <c r="J5">
+        <v>-0.01059144362807274</v>
+      </c>
+      <c r="K5">
+        <v>-0.9021078944206238</v>
+      </c>
+      <c r="L5">
+        <v>3.832185745239258</v>
+      </c>
+      <c r="M5">
+        <v>-0.6062155961990356</v>
+      </c>
+      <c r="N5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O5" t="s">
+        <v>192</v>
+      </c>
+      <c r="P5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.00739138832753692</v>
+      </c>
+      <c r="D6">
+        <v>0.003806336550042033</v>
+      </c>
+      <c r="E6">
+        <v>0.02665654197335243</v>
+      </c>
+      <c r="F6">
+        <v>0.001779828802682459</v>
+      </c>
+      <c r="G6">
+        <v>0.00151843496132642</v>
+      </c>
+      <c r="H6">
+        <v>1.001031997529998</v>
+      </c>
+      <c r="I6">
+        <v>0.049158447772418</v>
+      </c>
+      <c r="J6">
+        <v>0.1427918374538422</v>
+      </c>
+      <c r="K6">
+        <v>254214.9375</v>
+      </c>
+      <c r="L6">
+        <v>1.525723218917847</v>
+      </c>
+      <c r="M6">
+        <v>8.172883987426758</v>
+      </c>
+      <c r="N6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01465838310142689</v>
+      </c>
+      <c r="D7">
+        <v>0.007752592209726572</v>
+      </c>
+      <c r="E7">
+        <v>0.05345585569739342</v>
+      </c>
+      <c r="F7">
+        <v>0.002163931727409363</v>
+      </c>
+      <c r="G7">
+        <v>0.001766457105986774</v>
+      </c>
+      <c r="H7">
+        <v>1.000832905861147</v>
+      </c>
+      <c r="I7">
+        <v>0.04936112165086729</v>
+      </c>
+      <c r="J7">
+        <v>0.1450279355049133</v>
+      </c>
+      <c r="K7">
+        <v>97135493120</v>
+      </c>
+      <c r="L7">
+        <v>3.059618234634399</v>
+      </c>
+      <c r="M7">
+        <v>8.300869941711426</v>
+      </c>
+      <c r="N7" t="s">
+        <v>134</v>
+      </c>
+      <c r="O7" t="s">
+        <v>194</v>
+      </c>
+      <c r="P7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.03619567624408129</v>
+      </c>
+      <c r="D8">
+        <v>0.01928267814218998</v>
+      </c>
+      <c r="E8">
+        <v>0.1334642916917801</v>
+      </c>
+      <c r="F8">
+        <v>0.00240697804838419</v>
+      </c>
+      <c r="G8">
+        <v>0.002037846716120839</v>
+      </c>
+      <c r="H8">
+        <v>1.000426401139837</v>
+      </c>
+      <c r="I8">
+        <v>0.0511445768914499</v>
+      </c>
+      <c r="J8">
+        <v>0.1444781869649887</v>
+      </c>
+      <c r="K8">
+        <v>1.490327506258159E+27</v>
+      </c>
+      <c r="L8">
+        <v>7.63900899887085</v>
+      </c>
+      <c r="M8">
+        <v>8.269404411315918</v>
+      </c>
+      <c r="N8" t="s">
+        <v>135</v>
+      </c>
+      <c r="O8" t="s">
+        <v>195</v>
+      </c>
+      <c r="P8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.07193031177711291</v>
+      </c>
+      <c r="D9">
+        <v>0.03822388499975204</v>
+      </c>
+      <c r="E9">
+        <v>0.2670351564884186</v>
+      </c>
+      <c r="F9">
+        <v>0.002289796946570277</v>
+      </c>
+      <c r="G9">
+        <v>0.00192112463992089</v>
+      </c>
+      <c r="H9">
+        <v>0.9999820339968468</v>
+      </c>
+      <c r="I9">
+        <v>0.05314680587402754</v>
+      </c>
+      <c r="J9">
+        <v>0.1431417763233185</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>15.28411769866943</v>
+      </c>
+      <c r="M9">
+        <v>8.192913055419922</v>
+      </c>
+      <c r="N9" t="s">
+        <v>136</v>
+      </c>
+      <c r="O9" t="s">
+        <v>196</v>
+      </c>
+      <c r="P9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.1798533678080184</v>
+      </c>
+      <c r="D10">
+        <v>0.09536334872245789</v>
+      </c>
+      <c r="E10">
+        <v>0.6780470609664917</v>
+      </c>
+      <c r="F10">
+        <v>0.002093117218464613</v>
+      </c>
+      <c r="G10">
+        <v>0.00190857402049005</v>
+      </c>
+      <c r="H10">
+        <v>1.000823610294235</v>
+      </c>
+      <c r="I10">
+        <v>0.05839376985735346</v>
+      </c>
+      <c r="J10">
+        <v>0.1406441479921341</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>38.80894088745117</v>
+      </c>
+      <c r="M10">
+        <v>8.049958229064941</v>
+      </c>
+      <c r="N10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s">
+        <v>197</v>
+      </c>
+      <c r="P10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.3509997875355853</v>
+      </c>
+      <c r="D11">
+        <v>0.1859438717365265</v>
+      </c>
+      <c r="E11">
+        <v>1.257593631744385</v>
+      </c>
+      <c r="F11">
+        <v>0.002005635993555188</v>
+      </c>
+      <c r="G11">
+        <v>0.002050978830084205</v>
+      </c>
+      <c r="H11">
+        <v>1.002050183598531</v>
+      </c>
+      <c r="I11">
+        <v>0.06753264005703871</v>
+      </c>
+      <c r="J11">
+        <v>0.1478568762540817</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>71.98007202148438</v>
+      </c>
+      <c r="M11">
+        <v>8.462787628173828</v>
+      </c>
+      <c r="N11" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.00171963654621243</v>
+      </c>
+      <c r="D12">
+        <v>-0.0002993750676978379</v>
+      </c>
+      <c r="E12">
+        <v>0.01163668464869261</v>
+      </c>
+      <c r="F12">
+        <v>0.0007447429816238582</v>
+      </c>
+      <c r="G12">
+        <v>0.0007996588246896863</v>
+      </c>
+      <c r="H12">
+        <v>1.000559776864355</v>
+      </c>
+      <c r="I12">
+        <v>0.04892993209192245</v>
+      </c>
+      <c r="J12">
+        <v>-0.02572683431208134</v>
+      </c>
+      <c r="K12">
+        <v>-0.6250498294830322</v>
+      </c>
+      <c r="L12">
+        <v>0.666041374206543</v>
+      </c>
+      <c r="M12">
+        <v>-1.472510099411011</v>
+      </c>
+      <c r="N12" t="s">
+        <v>139</v>
+      </c>
+      <c r="O12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.002290114990207669</v>
+      </c>
+      <c r="D13">
+        <v>0.0002309125993633643</v>
+      </c>
+      <c r="E13">
+        <v>0.01514204498380423</v>
+      </c>
+      <c r="F13">
+        <v>0.0008417160133831203</v>
+      </c>
+      <c r="G13">
+        <v>0.000835843151435256</v>
+      </c>
+      <c r="H13">
+        <v>1.000832711484693</v>
+      </c>
+      <c r="I13">
+        <v>0.04885651861441255</v>
+      </c>
+      <c r="J13">
+        <v>0.01524976268410683</v>
+      </c>
+      <c r="K13">
+        <v>1.130525350570679</v>
+      </c>
+      <c r="L13">
+        <v>0.8666753768920898</v>
+      </c>
+      <c r="M13">
+        <v>0.8728407621383667</v>
+      </c>
+      <c r="N13" t="s">
+        <v>140</v>
+      </c>
+      <c r="O13" t="s">
+        <v>200</v>
+      </c>
+      <c r="P13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.00285927247340059</v>
+      </c>
+      <c r="D14">
+        <v>0.0008458672091364861</v>
+      </c>
+      <c r="E14">
+        <v>0.01792562380433083</v>
+      </c>
+      <c r="F14">
+        <v>0.0009279628284275532</v>
+      </c>
+      <c r="G14">
+        <v>0.0009034811519086361</v>
+      </c>
+      <c r="H14">
+        <v>1.00097081427031</v>
+      </c>
+      <c r="I14">
+        <v>0.04886519593367134</v>
+      </c>
+      <c r="J14">
+        <v>0.04718760401010513</v>
+      </c>
+      <c r="K14">
+        <v>14.95906257629395</v>
+      </c>
+      <c r="L14">
+        <v>1.025997281074524</v>
+      </c>
+      <c r="M14">
+        <v>2.700846195220947</v>
+      </c>
+      <c r="N14" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" t="s">
+        <v>201</v>
+      </c>
+      <c r="P14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.005700457620159539</v>
+      </c>
+      <c r="D15">
+        <v>0.002768519567325711</v>
+      </c>
+      <c r="E15">
+        <v>0.0357523076236248</v>
+      </c>
+      <c r="F15">
+        <v>0.001338615082204342</v>
+      </c>
+      <c r="G15">
+        <v>0.001255855895578861</v>
+      </c>
+      <c r="H15">
+        <v>1.001046885142443</v>
+      </c>
+      <c r="I15">
+        <v>0.04891578039825505</v>
+      </c>
+      <c r="J15">
+        <v>0.07743611186742783</v>
+      </c>
+      <c r="K15">
+        <v>8578.4794921875</v>
+      </c>
+      <c r="L15">
+        <v>2.046331644058228</v>
+      </c>
+      <c r="M15">
+        <v>4.432160377502441</v>
+      </c>
+      <c r="N15" t="s">
+        <v>142</v>
+      </c>
+      <c r="O15" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.01133680666134857</v>
+      </c>
+      <c r="D16">
+        <v>0.006103530991822481</v>
+      </c>
+      <c r="E16">
+        <v>0.07141619920730591</v>
+      </c>
+      <c r="F16">
+        <v>0.001823821221478283</v>
+      </c>
+      <c r="G16">
+        <v>0.001555043971166015</v>
+      </c>
+      <c r="H16">
+        <v>1.001021226552341</v>
+      </c>
+      <c r="I16">
+        <v>0.04917360156356629</v>
+      </c>
+      <c r="J16">
+        <v>0.0854642391204834</v>
+      </c>
+      <c r="K16">
+        <v>454334432</v>
+      </c>
+      <c r="L16">
+        <v>4.087602615356445</v>
+      </c>
+      <c r="M16">
+        <v>4.891661167144775</v>
+      </c>
+      <c r="N16" t="s">
+        <v>143</v>
+      </c>
+      <c r="O16" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.02248406349323057</v>
+      </c>
+      <c r="D17">
+        <v>0.01225396618247032</v>
+      </c>
+      <c r="E17">
+        <v>0.1422319263219833</v>
+      </c>
+      <c r="F17">
+        <v>0.00225431309081614</v>
+      </c>
+      <c r="G17">
+        <v>0.001811297843232751</v>
+      </c>
+      <c r="H17">
+        <v>1.000833378962084</v>
+      </c>
+      <c r="I17">
+        <v>0.0493465394295597</v>
+      </c>
+      <c r="J17">
+        <v>0.08615481853485107</v>
+      </c>
+      <c r="K17">
+        <v>2.130133354513695E+17</v>
+      </c>
+      <c r="L17">
+        <v>8.140836715698242</v>
+      </c>
+      <c r="M17">
+        <v>4.931187629699707</v>
+      </c>
+      <c r="N17" t="s">
+        <v>144</v>
+      </c>
+      <c r="O17" t="s">
+        <v>204</v>
+      </c>
+      <c r="P17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.05587693931683389</v>
+      </c>
+      <c r="D18">
+        <v>0.03041710890829563</v>
+      </c>
+      <c r="E18">
+        <v>0.3570390045642853</v>
+      </c>
+      <c r="F18">
+        <v>0.002437533810734749</v>
+      </c>
+      <c r="G18">
+        <v>0.00204862654209137</v>
+      </c>
+      <c r="H18">
+        <v>1.000384631951323</v>
+      </c>
+      <c r="I18">
+        <v>0.05117368314862971</v>
+      </c>
+      <c r="J18">
+        <v>0.08519268035888672</v>
+      </c>
+      <c r="K18" t="s">
+        <v>128</v>
+      </c>
+      <c r="L18">
+        <v>20.43560981750488</v>
+      </c>
+      <c r="M18">
+        <v>4.876118183135986</v>
+      </c>
+      <c r="N18" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" t="s">
+        <v>205</v>
+      </c>
+      <c r="P18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.1100926478304901</v>
+      </c>
+      <c r="D19">
+        <v>0.05976492166519165</v>
+      </c>
+      <c r="E19">
+        <v>0.6993597745895386</v>
+      </c>
+      <c r="F19">
+        <v>0.002273583086207509</v>
+      </c>
+      <c r="G19">
+        <v>0.001906360499560833</v>
+      </c>
+      <c r="H19">
+        <v>0.9998956831348585</v>
+      </c>
+      <c r="I19">
+        <v>0.05328389567831149</v>
+      </c>
+      <c r="J19">
+        <v>0.08545661717653275</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>40.02880096435547</v>
+      </c>
+      <c r="M19">
+        <v>4.89122486114502</v>
+      </c>
+      <c r="N19" t="s">
+        <v>146</v>
+      </c>
+      <c r="O19" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.2772944055409443</v>
+      </c>
+      <c r="D20">
+        <v>0.1502858251333237</v>
+      </c>
+      <c r="E20">
+        <v>1.784477353096008</v>
+      </c>
+      <c r="F20">
+        <v>0.002096183830872178</v>
+      </c>
+      <c r="G20">
+        <v>0.001901404350064695</v>
+      </c>
+      <c r="H20">
+        <v>1.000687611382226</v>
+      </c>
+      <c r="I20">
+        <v>0.05884718697272701</v>
+      </c>
+      <c r="J20">
+        <v>0.08421839773654938</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>102.1369705200195</v>
+      </c>
+      <c r="M20">
+        <v>4.820353984832764</v>
+      </c>
+      <c r="N20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20" t="s">
+        <v>207</v>
+      </c>
+      <c r="P20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.5298017733541837</v>
+      </c>
+      <c r="D21">
+        <v>0.2867112159729004</v>
+      </c>
+      <c r="E21">
+        <v>3.241537809371948</v>
+      </c>
+      <c r="F21">
+        <v>0.001993259647861123</v>
+      </c>
+      <c r="G21">
+        <v>0.002003053901717067</v>
+      </c>
+      <c r="H21">
+        <v>1.002050183598531</v>
+      </c>
+      <c r="I21">
+        <v>0.06753264005703871</v>
+      </c>
+      <c r="J21">
+        <v>0.0884491354227066</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>185.5337982177734</v>
+      </c>
+      <c r="M21">
+        <v>5.062505722045898</v>
+      </c>
+      <c r="N21" t="s">
+        <v>148</v>
+      </c>
+      <c r="O21" t="s">
+        <v>208</v>
+      </c>
+      <c r="P21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0007669014320297315</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003820675192400813</v>
+      </c>
+      <c r="E22">
+        <v>0.00315646012313664</v>
+      </c>
+      <c r="F22">
+        <v>0.0007397022563964128</v>
+      </c>
+      <c r="G22">
+        <v>0.0007806574576534331</v>
+      </c>
+      <c r="H22">
+        <v>1.000538836161631</v>
+      </c>
+      <c r="I22">
+        <v>0.04892819239218498</v>
+      </c>
+      <c r="J22">
+        <v>-0.1210430338978767</v>
+      </c>
+      <c r="K22">
+        <v>-0.7140352129936218</v>
+      </c>
+      <c r="L22">
+        <v>0.1806642562150955</v>
+      </c>
+      <c r="M22">
+        <v>-6.928061485290527</v>
+      </c>
+      <c r="N22" t="s">
+        <v>149</v>
+      </c>
+      <c r="O22" t="s">
+        <v>209</v>
+      </c>
+      <c r="P22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.001019892258704085</v>
+      </c>
+      <c r="D23">
+        <v>-8.573324157623574E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.00413090456277132</v>
+      </c>
+      <c r="F23">
+        <v>0.0008429762674495578</v>
+      </c>
+      <c r="G23">
+        <v>0.000831877812743187</v>
+      </c>
+      <c r="H23">
+        <v>1.000789008044175</v>
+      </c>
+      <c r="I23">
+        <v>0.0488871192666562</v>
+      </c>
+      <c r="J23">
+        <v>-0.02075410820543766</v>
+      </c>
+      <c r="K23">
+        <v>-0.2448228001594543</v>
+      </c>
+      <c r="L23">
+        <v>0.2364379018545151</v>
+      </c>
+      <c r="M23">
+        <v>-1.187889456748962</v>
+      </c>
+      <c r="N23" t="s">
+        <v>150</v>
+      </c>
+      <c r="O23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.001271754714832058</v>
+      </c>
+      <c r="D24">
+        <v>0.000171854073414579</v>
+      </c>
+      <c r="E24">
+        <v>0.005071163643151522</v>
+      </c>
+      <c r="F24">
+        <v>0.0009463241440244019</v>
+      </c>
+      <c r="G24">
+        <v>0.0009222057997249067</v>
+      </c>
+      <c r="H24">
+        <v>1.000923317370322</v>
+      </c>
+      <c r="I24">
+        <v>0.04888162988242156</v>
+      </c>
+      <c r="J24">
+        <v>0.03388848900794983</v>
+      </c>
+      <c r="K24">
+        <v>0.7560998201370239</v>
+      </c>
+      <c r="L24">
+        <v>0.2902548909187317</v>
+      </c>
+      <c r="M24">
+        <v>1.939653396606445</v>
+      </c>
+      <c r="N24" t="s">
+        <v>151</v>
+      </c>
+      <c r="O24" t="s">
+        <v>211</v>
+      </c>
+      <c r="P24" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.002518269895164136</v>
+      </c>
+      <c r="D25">
+        <v>0.001123599708080292</v>
+      </c>
+      <c r="E25">
+        <v>0.009604261256754398</v>
+      </c>
+      <c r="F25">
+        <v>0.001396413776092231</v>
+      </c>
+      <c r="G25">
+        <v>0.001287734252400696</v>
+      </c>
+      <c r="H25">
+        <v>1.000980534380253</v>
+      </c>
+      <c r="I25">
+        <v>0.04896734658291906</v>
+      </c>
+      <c r="J25">
+        <v>0.1169897094368935</v>
+      </c>
+      <c r="K25">
+        <v>38.59392166137695</v>
+      </c>
+      <c r="L25">
+        <v>0.5497128963470459</v>
+      </c>
+      <c r="M25">
+        <v>6.696063995361328</v>
+      </c>
+      <c r="N25" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" t="s">
+        <v>212</v>
+      </c>
+      <c r="P25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.004961265000080945</v>
+      </c>
+      <c r="D26">
+        <v>0.002503691473975778</v>
+      </c>
+      <c r="E26">
+        <v>0.01912158355116844</v>
+      </c>
+      <c r="F26">
+        <v>0.001904209959320724</v>
+      </c>
+      <c r="G26">
+        <v>0.001612233812920749</v>
+      </c>
+      <c r="H26">
+        <v>1.00101770963196</v>
+      </c>
+      <c r="I26">
+        <v>0.04919277452394859</v>
+      </c>
+      <c r="J26">
+        <v>0.1309353560209274</v>
+      </c>
+      <c r="K26">
+        <v>3609.686279296875</v>
+      </c>
+      <c r="L26">
+        <v>1.094449639320374</v>
+      </c>
+      <c r="M26">
+        <v>7.494262218475342</v>
+      </c>
+      <c r="N26" t="s">
+        <v>153</v>
+      </c>
+      <c r="O26" t="s">
+        <v>213</v>
+      </c>
+      <c r="P26" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.009758129642096434</v>
+      </c>
+      <c r="D27">
+        <v>0.005241482518613338</v>
+      </c>
+      <c r="E27">
+        <v>0.03778624907135963</v>
+      </c>
+      <c r="F27">
+        <v>0.00232591456733644</v>
+      </c>
+      <c r="G27">
+        <v>0.001877642120234668</v>
+      </c>
+      <c r="H27">
+        <v>1.000765204317129</v>
+      </c>
+      <c r="I27">
+        <v>0.04940385503192391</v>
+      </c>
+      <c r="J27">
+        <v>0.1387140154838562</v>
+      </c>
+      <c r="K27">
+        <v>27408192</v>
+      </c>
+      <c r="L27">
+        <v>2.162746906280518</v>
+      </c>
+      <c r="M27">
+        <v>7.939484119415283</v>
+      </c>
+      <c r="N27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O27" t="s">
+        <v>214</v>
+      </c>
+      <c r="P27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.02392081288051207</v>
+      </c>
+      <c r="D28">
+        <v>0.01268630474805832</v>
+      </c>
+      <c r="E28">
+        <v>0.09412854164838791</v>
+      </c>
+      <c r="F28">
+        <v>0.002441259566694498</v>
+      </c>
+      <c r="G28">
+        <v>0.002059967489913106</v>
+      </c>
+      <c r="H28">
+        <v>1.000384436864432</v>
+      </c>
+      <c r="I28">
+        <v>0.05123974018586073</v>
+      </c>
+      <c r="J28">
+        <v>0.134776383638382</v>
+      </c>
+      <c r="K28">
+        <v>8.626200608652657E+17</v>
+      </c>
+      <c r="L28">
+        <v>5.387574195861816</v>
+      </c>
+      <c r="M28">
+        <v>7.714108467102051</v>
+      </c>
+      <c r="N28" t="s">
+        <v>155</v>
+      </c>
+      <c r="O28" t="s">
+        <v>215</v>
+      </c>
+      <c r="P28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.04761473534077544</v>
+      </c>
+      <c r="D29">
+        <v>0.02506129816174507</v>
+      </c>
+      <c r="E29">
+        <v>0.1913139671087265</v>
+      </c>
+      <c r="F29">
+        <v>0.002240500180050731</v>
+      </c>
+      <c r="G29">
+        <v>0.001920918584801257</v>
+      </c>
+      <c r="H29">
+        <v>0.9999807928435912</v>
+      </c>
+      <c r="I29">
+        <v>0.05318358775775955</v>
+      </c>
+      <c r="J29">
+        <v>0.1309956610202789</v>
+      </c>
+      <c r="K29">
+        <v>1.645879410783123E+35</v>
+      </c>
+      <c r="L29">
+        <v>10.95011329650879</v>
+      </c>
+      <c r="M29">
+        <v>7.497713565826416</v>
+      </c>
+      <c r="N29" t="s">
+        <v>156</v>
+      </c>
+      <c r="O29" t="s">
+        <v>216</v>
+      </c>
+      <c r="P29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.1168463829259604</v>
+      </c>
+      <c r="D30">
+        <v>0.06099297106266022</v>
+      </c>
+      <c r="E30">
+        <v>0.4681063890457153</v>
+      </c>
+      <c r="F30">
+        <v>0.002040160121396184</v>
+      </c>
+      <c r="G30">
+        <v>0.001919956761412323</v>
+      </c>
+      <c r="H30">
+        <v>1.000687611382226</v>
+      </c>
+      <c r="I30">
+        <v>0.05884718697272701</v>
+      </c>
+      <c r="J30">
+        <v>0.1302972435951233</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>26.79270172119141</v>
+      </c>
+      <c r="M30">
+        <v>7.457738876342773</v>
+      </c>
+      <c r="N30" t="s">
+        <v>157</v>
+      </c>
+      <c r="O30" t="s">
+        <v>217</v>
+      </c>
+      <c r="P30" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.2389244792153188</v>
+      </c>
+      <c r="D31">
+        <v>0.1268303543329239</v>
+      </c>
+      <c r="E31">
+        <v>1.018275380134583</v>
+      </c>
+      <c r="F31">
+        <v>0.001987117109820247</v>
+      </c>
+      <c r="G31">
+        <v>0.002081617945805192</v>
+      </c>
+      <c r="H31">
+        <v>1.001774785801714</v>
+      </c>
+      <c r="I31">
+        <v>0.06859257480808534</v>
+      </c>
+      <c r="J31">
+        <v>0.1245540827512741</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>58.28236770629883</v>
+      </c>
+      <c r="M31">
+        <v>7.129021167755127</v>
+      </c>
+      <c r="N31" t="s">
+        <v>158</v>
+      </c>
+      <c r="O31" t="s">
+        <v>218</v>
+      </c>
+      <c r="P31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.0006048199575876627</v>
+      </c>
+      <c r="D32">
+        <v>-0.0001214440926560201</v>
+      </c>
+      <c r="E32">
+        <v>0.003272154601290822</v>
+      </c>
+      <c r="F32">
+        <v>0.0007411091355606914</v>
+      </c>
+      <c r="G32">
+        <v>0.0007763634785078466</v>
+      </c>
+      <c r="H32">
+        <v>1.000471580260223</v>
+      </c>
+      <c r="I32">
+        <v>0.04896425088180852</v>
+      </c>
+      <c r="J32">
+        <v>-0.03711441159248352</v>
+      </c>
+      <c r="K32">
+        <v>-0.3281892538070679</v>
+      </c>
+      <c r="L32">
+        <v>0.1872861832380295</v>
+      </c>
+      <c r="M32">
+        <v>-2.124293565750122</v>
+      </c>
+      <c r="N32" t="s">
+        <v>159</v>
+      </c>
+      <c r="O32" t="s">
+        <v>219</v>
+      </c>
+      <c r="P32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0008034787775060087</v>
+      </c>
+      <c r="D33">
+        <v>0.0001111407327698544</v>
+      </c>
+      <c r="E33">
+        <v>0.004273331258445978</v>
+      </c>
+      <c r="F33">
+        <v>0.0008633336401544511</v>
+      </c>
+      <c r="G33">
+        <v>0.0008468133746646345</v>
+      </c>
+      <c r="H33">
+        <v>1.000682427189011</v>
+      </c>
+      <c r="I33">
+        <v>0.04891014369297138</v>
+      </c>
+      <c r="J33">
+        <v>0.02600798383355141</v>
+      </c>
+      <c r="K33">
+        <v>0.4390071630477905</v>
+      </c>
+      <c r="L33">
+        <v>0.2445898950099945</v>
+      </c>
+      <c r="M33">
+        <v>1.488602042198181</v>
+      </c>
+      <c r="N33" t="s">
+        <v>160</v>
+      </c>
+      <c r="O33" t="s">
+        <v>220</v>
+      </c>
+      <c r="P33" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.001000687452421256</v>
+      </c>
+      <c r="D34">
+        <v>0.0002998802228830755</v>
+      </c>
+      <c r="E34">
+        <v>0.005315890535712242</v>
+      </c>
+      <c r="F34">
+        <v>0.0009828931652009487</v>
+      </c>
+      <c r="G34">
+        <v>0.0009461453882977366</v>
+      </c>
+      <c r="H34">
+        <v>1.000778041884807</v>
+      </c>
+      <c r="I34">
+        <v>0.04892787709493223</v>
+      </c>
+      <c r="J34">
+        <v>0.05641203746199608</v>
+      </c>
+      <c r="K34">
+        <v>1.670926094055176</v>
+      </c>
+      <c r="L34">
+        <v>0.3042621910572052</v>
+      </c>
+      <c r="M34">
+        <v>3.228819131851196</v>
+      </c>
+      <c r="N34" t="s">
+        <v>161</v>
+      </c>
+      <c r="O34" t="s">
+        <v>221</v>
+      </c>
+      <c r="P34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.001970610262137675</v>
+      </c>
+      <c r="D35">
+        <v>0.0009846213506534696</v>
+      </c>
+      <c r="E35">
+        <v>0.01054634992033243</v>
+      </c>
+      <c r="F35">
+        <v>0.001470223069190979</v>
+      </c>
+      <c r="G35">
+        <v>0.001320981071330607</v>
+      </c>
+      <c r="H35">
+        <v>1.000895272533523</v>
+      </c>
+      <c r="I35">
+        <v>0.04897515623902261</v>
+      </c>
+      <c r="J35">
+        <v>0.09336134046316147</v>
+      </c>
+      <c r="K35">
+        <v>24.13314819335938</v>
+      </c>
+      <c r="L35">
+        <v>0.6036345958709717</v>
+      </c>
+      <c r="M35">
+        <v>5.343662261962891</v>
+      </c>
+      <c r="N35" t="s">
+        <v>162</v>
+      </c>
+      <c r="O35" t="s">
+        <v>222</v>
+      </c>
+      <c r="P35" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.003854715912008116</v>
+      </c>
+      <c r="D36">
+        <v>0.002149879466742277</v>
+      </c>
+      <c r="E36">
+        <v>0.02083710208535194</v>
+      </c>
+      <c r="F36">
+        <v>0.001995171653106809</v>
+      </c>
+      <c r="G36">
+        <v>0.00165925663895905</v>
+      </c>
+      <c r="H36">
+        <v>1.000947231805581</v>
+      </c>
+      <c r="I36">
+        <v>0.04921534659423025</v>
+      </c>
+      <c r="J36">
+        <v>0.103175550699234</v>
+      </c>
+      <c r="K36">
+        <v>1134.98095703125</v>
+      </c>
+      <c r="L36">
+        <v>1.192639708518982</v>
+      </c>
+      <c r="M36">
+        <v>5.905392169952393</v>
+      </c>
+      <c r="N36" t="s">
+        <v>163</v>
+      </c>
+      <c r="O36" t="s">
+        <v>223</v>
+      </c>
+      <c r="P36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.007514815814433398</v>
+      </c>
+      <c r="D37">
+        <v>0.004175666719675064</v>
+      </c>
+      <c r="E37">
+        <v>0.04163314402103424</v>
+      </c>
+      <c r="F37">
+        <v>0.002408575965091586</v>
+      </c>
+      <c r="G37">
+        <v>0.001943595823831856</v>
+      </c>
+      <c r="H37">
+        <v>1.000707792431533</v>
+      </c>
+      <c r="I37">
+        <v>0.04938980115709161</v>
+      </c>
+      <c r="J37">
+        <v>0.1002966910600662</v>
+      </c>
+      <c r="K37">
+        <v>848300</v>
+      </c>
+      <c r="L37">
+        <v>2.38292932510376</v>
+      </c>
+      <c r="M37">
+        <v>5.740616798400879</v>
+      </c>
+      <c r="N37" t="s">
+        <v>164</v>
+      </c>
+      <c r="O37" t="s">
+        <v>224</v>
+      </c>
+      <c r="P37" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.01829732926124212</v>
+      </c>
+      <c r="D38">
+        <v>0.009868361055850983</v>
+      </c>
+      <c r="E38">
+        <v>0.1040614321827888</v>
+      </c>
+      <c r="F38">
+        <v>0.0024536841083318</v>
+      </c>
+      <c r="G38">
+        <v>0.002026650821790099</v>
+      </c>
+      <c r="H38">
+        <v>1.000413704562405</v>
+      </c>
+      <c r="I38">
+        <v>0.05123588922525264</v>
+      </c>
+      <c r="J38">
+        <v>0.09483207017183304</v>
+      </c>
+      <c r="K38">
+        <v>93627862745088</v>
+      </c>
+      <c r="L38">
+        <v>5.956096649169922</v>
+      </c>
+      <c r="M38">
+        <v>5.427841663360596</v>
+      </c>
+      <c r="N38" t="s">
+        <v>165</v>
+      </c>
+      <c r="O38" t="s">
+        <v>225</v>
+      </c>
+      <c r="P38" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.03611880267192333</v>
+      </c>
+      <c r="D39">
+        <v>0.01923673413693905</v>
+      </c>
+      <c r="E39">
+        <v>0.2081621140241623</v>
+      </c>
+      <c r="F39">
+        <v>0.002207066398113966</v>
+      </c>
+      <c r="G39">
+        <v>0.001879711984656751</v>
+      </c>
+      <c r="H39">
+        <v>0.9998954619734433</v>
+      </c>
+      <c r="I39">
+        <v>0.05354284586723794</v>
+      </c>
+      <c r="J39">
+        <v>0.09241227060556412</v>
+      </c>
+      <c r="K39">
+        <v>1.285438486813799E+27</v>
+      </c>
+      <c r="L39">
+        <v>11.9144401550293</v>
+      </c>
+      <c r="M39">
+        <v>5.289340972900391</v>
+      </c>
+      <c r="N39" t="s">
+        <v>166</v>
+      </c>
+      <c r="O39" t="s">
+        <v>226</v>
+      </c>
+      <c r="P39" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.08798682663370944</v>
+      </c>
+      <c r="D40">
+        <v>0.046393983066082</v>
+      </c>
+      <c r="E40">
+        <v>0.5075863003730774</v>
+      </c>
+      <c r="F40">
+        <v>0.002006604569032788</v>
+      </c>
+      <c r="G40">
+        <v>0.001858551288023591</v>
+      </c>
+      <c r="H40">
+        <v>1.000619611926221</v>
+      </c>
+      <c r="I40">
+        <v>0.05894427491670855</v>
+      </c>
+      <c r="J40">
+        <v>0.09140117466449738</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>29.05238723754883</v>
+      </c>
+      <c r="M40">
+        <v>5.231469631195068</v>
+      </c>
+      <c r="N40" t="s">
+        <v>167</v>
+      </c>
+      <c r="O40" t="s">
+        <v>227</v>
+      </c>
+      <c r="P40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.183253135435312</v>
+      </c>
+      <c r="D41">
+        <v>0.09625311940908432</v>
+      </c>
+      <c r="E41">
+        <v>1.118601202964783</v>
+      </c>
+      <c r="F41">
+        <v>0.001980626722797751</v>
+      </c>
+      <c r="G41">
+        <v>0.002053971402347088</v>
+      </c>
+      <c r="H41">
+        <v>1.001376988984088</v>
+      </c>
+      <c r="I41">
+        <v>0.06970378012990126</v>
+      </c>
+      <c r="J41">
+        <v>0.08604775369167328</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>64.02465057373047</v>
+      </c>
+      <c r="M41">
+        <v>4.92505931854248</v>
+      </c>
+      <c r="N41" t="s">
+        <v>168</v>
+      </c>
+      <c r="O41" t="s">
+        <v>228</v>
+      </c>
+      <c r="P41" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.000219748170371757</v>
+      </c>
+      <c r="D42">
+        <v>-6.003737507853657E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001570629770867527</v>
+      </c>
+      <c r="F42">
+        <v>0.0007538858335465193</v>
+      </c>
+      <c r="G42">
+        <v>0.0007954727043397725</v>
+      </c>
+      <c r="H42">
+        <v>1.000344489422422</v>
+      </c>
+      <c r="I42">
+        <v>0.04902672213774145</v>
+      </c>
+      <c r="J42">
+        <v>-0.03822503238916397</v>
+      </c>
+      <c r="K42">
+        <v>-0.1785116791725159</v>
+      </c>
+      <c r="L42">
+        <v>0.08989711850881577</v>
+      </c>
+      <c r="M42">
+        <v>-2.187861442565918</v>
+      </c>
+      <c r="N42" t="s">
+        <v>169</v>
+      </c>
+      <c r="O42" t="s">
+        <v>229</v>
+      </c>
+      <c r="P42" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.0002889466044361597</v>
+      </c>
+      <c r="D43">
+        <v>4.175660433247685E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.002052253112196922</v>
+      </c>
+      <c r="F43">
+        <v>0.000908130663447082</v>
+      </c>
+      <c r="G43">
+        <v>0.0009035787079483271</v>
+      </c>
+      <c r="H43">
+        <v>1.000498889397033</v>
+      </c>
+      <c r="I43">
+        <v>0.04896058226629821</v>
+      </c>
+      <c r="J43">
+        <v>0.02034671232104301</v>
+      </c>
+      <c r="K43">
+        <v>0.1464641094207764</v>
+      </c>
+      <c r="L43">
+        <v>0.1174634769558907</v>
+      </c>
+      <c r="M43">
+        <v>1.164571523666382</v>
+      </c>
+      <c r="N43" t="s">
+        <v>170</v>
+      </c>
+      <c r="O43" t="s">
+        <v>230</v>
+      </c>
+      <c r="P43" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0003560010738840662</v>
+      </c>
+      <c r="D44">
+        <v>0.0001314988185185939</v>
+      </c>
+      <c r="E44">
+        <v>0.002422111108899117</v>
+      </c>
+      <c r="F44">
+        <v>0.001044609700329602</v>
+      </c>
+      <c r="G44">
+        <v>0.001028012949973345</v>
+      </c>
+      <c r="H44">
+        <v>1.00058057996151</v>
+      </c>
+      <c r="I44">
+        <v>0.04898251810100586</v>
+      </c>
+      <c r="J44">
+        <v>0.05429099500179291</v>
+      </c>
+      <c r="K44">
+        <v>0.5383738279342651</v>
+      </c>
+      <c r="L44">
+        <v>0.1386328041553497</v>
+      </c>
+      <c r="M44">
+        <v>3.107418537139893</v>
+      </c>
+      <c r="N44" t="s">
+        <v>171</v>
+      </c>
+      <c r="O44" t="s">
+        <v>231</v>
+      </c>
+      <c r="P44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.0006703641633815394</v>
+      </c>
+      <c r="D45">
+        <v>0.0004950685543008149</v>
+      </c>
+      <c r="E45">
+        <v>0.003186209592968225</v>
+      </c>
+      <c r="F45">
+        <v>0.001592534361407161</v>
+      </c>
+      <c r="G45">
+        <v>0.001376014086417854</v>
+      </c>
+      <c r="H45">
+        <v>1.000766747699353</v>
+      </c>
+      <c r="I45">
+        <v>0.04903637115583991</v>
+      </c>
+      <c r="J45">
+        <v>0.155378520488739</v>
+      </c>
+      <c r="K45">
+        <v>4.0605149269104</v>
+      </c>
+      <c r="L45">
+        <v>0.1823670119047165</v>
+      </c>
+      <c r="M45">
+        <v>8.893299102783203</v>
+      </c>
+      <c r="N45" t="s">
+        <v>172</v>
+      </c>
+      <c r="O45" t="s">
+        <v>232</v>
+      </c>
+      <c r="P45" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.001226743966467516</v>
+      </c>
+      <c r="D46">
+        <v>0.0008802482625469565</v>
+      </c>
+      <c r="E46">
+        <v>0.006188403349369764</v>
+      </c>
+      <c r="F46">
+        <v>0.002131839049980044</v>
+      </c>
+      <c r="G46">
+        <v>0.001739437691867352</v>
+      </c>
+      <c r="H46">
+        <v>1.000856566362794</v>
+      </c>
+      <c r="I46">
+        <v>0.04920907994731985</v>
+      </c>
+      <c r="J46">
+        <v>0.142241582274437</v>
+      </c>
+      <c r="K46">
+        <v>16.85712051391602</v>
+      </c>
+      <c r="L46">
+        <v>0.35420161485672</v>
+      </c>
+      <c r="M46">
+        <v>8.141388893127441</v>
+      </c>
+      <c r="N46" t="s">
+        <v>173</v>
+      </c>
+      <c r="O46" t="s">
+        <v>233</v>
+      </c>
+      <c r="P46" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.002232793675531043</v>
+      </c>
+      <c r="D47">
+        <v>0.001474218443036079</v>
+      </c>
+      <c r="E47">
+        <v>0.01220789458602667</v>
+      </c>
+      <c r="F47">
+        <v>0.002546301344409585</v>
+      </c>
+      <c r="G47">
+        <v>0.002055392367765307</v>
+      </c>
+      <c r="H47">
+        <v>1.000598355280036</v>
+      </c>
+      <c r="I47">
+        <v>0.04948858967753336</v>
+      </c>
+      <c r="J47">
+        <v>0.1207594349980354</v>
+      </c>
+      <c r="K47">
+        <v>123.7265014648438</v>
+      </c>
+      <c r="L47">
+        <v>0.6987353563308716</v>
+      </c>
+      <c r="M47">
+        <v>6.911829471588135</v>
+      </c>
+      <c r="N47" t="s">
+        <v>174</v>
+      </c>
+      <c r="O47" t="s">
+        <v>234</v>
+      </c>
+      <c r="P47" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.005024943798898932</v>
+      </c>
+      <c r="D48">
+        <v>0.002968801651149988</v>
+      </c>
+      <c r="E48">
+        <v>0.03023136779665947</v>
+      </c>
+      <c r="F48">
+        <v>0.002410621382296085</v>
+      </c>
+      <c r="G48">
+        <v>0.002002348192036152</v>
+      </c>
+      <c r="H48">
+        <v>1.000240121153199</v>
+      </c>
+      <c r="I48">
+        <v>0.05135665104444152</v>
+      </c>
+      <c r="J48">
+        <v>0.09820269048213959</v>
+      </c>
+      <c r="K48">
+        <v>16502.728515625</v>
+      </c>
+      <c r="L48">
+        <v>1.730333209037781</v>
+      </c>
+      <c r="M48">
+        <v>5.620763778686523</v>
+      </c>
+      <c r="N48" t="s">
+        <v>175</v>
+      </c>
+      <c r="O48" t="s">
+        <v>235</v>
+      </c>
+      <c r="P48" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.009529133087117144</v>
+      </c>
+      <c r="D49">
+        <v>0.005380084738135338</v>
+      </c>
+      <c r="E49">
+        <v>0.0604221411049366</v>
+      </c>
+      <c r="F49">
+        <v>0.002121243393048644</v>
+      </c>
+      <c r="G49">
+        <v>0.001834567403420806</v>
+      </c>
+      <c r="H49">
+        <v>0.9998653258508958</v>
+      </c>
+      <c r="I49">
+        <v>0.05357052117898859</v>
+      </c>
+      <c r="J49">
+        <v>0.08904161304235458</v>
+      </c>
+      <c r="K49">
+        <v>43044744</v>
+      </c>
+      <c r="L49">
+        <v>3.458342790603638</v>
+      </c>
+      <c r="M49">
+        <v>5.09641695022583</v>
+      </c>
+      <c r="N49" t="s">
+        <v>176</v>
+      </c>
+      <c r="O49" t="s">
+        <v>236</v>
+      </c>
+      <c r="P49" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.02305567027623775</v>
+      </c>
+      <c r="D50">
+        <v>0.01245862059295177</v>
+      </c>
+      <c r="E50">
+        <v>0.1557591706514359</v>
+      </c>
+      <c r="F50">
+        <v>0.001969702308997512</v>
+      </c>
+      <c r="G50">
+        <v>0.001976495608687401</v>
+      </c>
+      <c r="H50">
+        <v>1.000398613694207</v>
+      </c>
+      <c r="I50">
+        <v>0.05926814504724552</v>
+      </c>
+      <c r="J50">
+        <v>0.07998643070459366</v>
+      </c>
+      <c r="K50">
+        <v>4.129490452422328E+17</v>
+      </c>
+      <c r="L50">
+        <v>8.91508674621582</v>
+      </c>
+      <c r="M50">
+        <v>4.578131198883057</v>
+      </c>
+      <c r="N50" t="s">
+        <v>177</v>
+      </c>
+      <c r="O50" t="s">
+        <v>237</v>
+      </c>
+      <c r="P50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.0457409385234127</v>
+      </c>
+      <c r="D51">
+        <v>0.02441716752946377</v>
+      </c>
+      <c r="E51">
+        <v>0.3141548931598663</v>
+      </c>
+      <c r="F51">
+        <v>0.002044193912297487</v>
+      </c>
+      <c r="G51">
+        <v>0.002631651470437646</v>
+      </c>
+      <c r="H51">
+        <v>1.001499388004896</v>
+      </c>
+      <c r="I51">
+        <v>0.0694370201069663</v>
+      </c>
+      <c r="J51">
+        <v>0.07772333920001984</v>
+      </c>
+      <c r="K51">
+        <v>2.099645589419156E+34</v>
+      </c>
+      <c r="L51">
+        <v>17.9810791015625</v>
+      </c>
+      <c r="M51">
+        <v>4.448600292205811</v>
+      </c>
+      <c r="N51" t="s">
+        <v>178</v>
+      </c>
+      <c r="O51" t="s">
+        <v>238</v>
+      </c>
+      <c r="P51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.0001365046925981976</v>
+      </c>
+      <c r="D52">
+        <v>0.0002361400838708505</v>
+      </c>
+      <c r="E52">
+        <v>0.0007139315130189061</v>
+      </c>
+      <c r="F52">
+        <v>0.0009471433004364371</v>
+      </c>
+      <c r="G52">
+        <v>0.0008774871821515262</v>
+      </c>
+      <c r="H52">
+        <v>0.9996204630796437</v>
+      </c>
+      <c r="I52">
+        <v>0.04944786290083107</v>
+      </c>
+      <c r="J52">
+        <v>0.33076012134552</v>
+      </c>
+      <c r="K52">
+        <v>1.167442321777344</v>
+      </c>
+      <c r="L52">
+        <v>0.04086283594369888</v>
+      </c>
+      <c r="M52">
+        <v>18.93150329589844</v>
+      </c>
+      <c r="N52" t="s">
+        <v>179</v>
+      </c>
+      <c r="O52" t="s">
+        <v>239</v>
+      </c>
+      <c r="P52" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0001709559008370167</v>
+      </c>
+      <c r="D53">
+        <v>0.0002870159514714032</v>
+      </c>
+      <c r="E53">
+        <v>0.0007578687509521842</v>
+      </c>
+      <c r="F53">
+        <v>0.001161839929409325</v>
+      </c>
+      <c r="G53">
+        <v>0.001094611128792167</v>
+      </c>
+      <c r="H53">
+        <v>1.000052901605951</v>
+      </c>
+      <c r="I53">
+        <v>0.04924805346034485</v>
+      </c>
+      <c r="J53">
+        <v>0.3787145912647247</v>
+      </c>
+      <c r="K53">
+        <v>1.560648202896118</v>
+      </c>
+      <c r="L53">
+        <v>0.04337764158844948</v>
+      </c>
+      <c r="M53">
+        <v>21.67624092102051</v>
+      </c>
+      <c r="N53" t="s">
+        <v>180</v>
+      </c>
+      <c r="O53" t="s">
+        <v>240</v>
+      </c>
+      <c r="P53" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.0002017353346046278</v>
+      </c>
+      <c r="D54">
+        <v>0.0003284779086243361</v>
+      </c>
+      <c r="E54">
+        <v>0.0007903290097601712</v>
+      </c>
+      <c r="F54">
+        <v>0.001314476830884814</v>
+      </c>
+      <c r="G54">
+        <v>0.001218026969581842</v>
+      </c>
+      <c r="H54">
+        <v>1.000360458425384</v>
+      </c>
+      <c r="I54">
+        <v>0.04914360439309099</v>
+      </c>
+      <c r="J54">
+        <v>0.4156217277050018</v>
+      </c>
+      <c r="K54">
+        <v>1.932139873504639</v>
+      </c>
+      <c r="L54">
+        <v>0.04523554816842079</v>
+      </c>
+      <c r="M54">
+        <v>23.78867149353027</v>
+      </c>
+      <c r="N54" t="s">
+        <v>181</v>
+      </c>
+      <c r="O54" t="s">
+        <v>241</v>
+      </c>
+      <c r="P54" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.0003150261449874445</v>
+      </c>
+      <c r="D55">
+        <v>0.0004590048338286579</v>
+      </c>
+      <c r="E55">
+        <v>0.000925256812479347</v>
+      </c>
+      <c r="F55">
+        <v>0.001725126639939845</v>
+      </c>
+      <c r="G55">
+        <v>0.0015239646891132</v>
+      </c>
+      <c r="H55">
+        <v>1.000599439617124</v>
+      </c>
+      <c r="I55">
+        <v>0.04920452529459642</v>
+      </c>
+      <c r="J55">
+        <v>0.4960837066173553</v>
+      </c>
+      <c r="K55">
+        <v>3.496026992797852</v>
+      </c>
+      <c r="L55">
+        <v>0.05295832455158234</v>
+      </c>
+      <c r="M55">
+        <v>28.39402198791504</v>
+      </c>
+      <c r="N55" t="s">
+        <v>182</v>
+      </c>
+      <c r="O55" t="s">
+        <v>242</v>
+      </c>
+      <c r="P55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0004394859908156978</v>
+      </c>
+      <c r="D56">
+        <v>0.0005954660591669381</v>
+      </c>
+      <c r="E56">
+        <v>0.001145415590144694</v>
+      </c>
+      <c r="F56">
+        <v>0.002371379639953375</v>
+      </c>
+      <c r="G56">
+        <v>0.001940853893756866</v>
+      </c>
+      <c r="H56">
+        <v>1.00051181047935</v>
+      </c>
+      <c r="I56">
+        <v>0.04963147510919678</v>
+      </c>
+      <c r="J56">
+        <v>0.5198690295219421</v>
+      </c>
+      <c r="K56">
+        <v>6.029495716094971</v>
+      </c>
+      <c r="L56">
+        <v>0.06555940955877304</v>
+      </c>
+      <c r="M56">
+        <v>29.75540542602539</v>
+      </c>
+      <c r="N56" t="s">
+        <v>183</v>
+      </c>
+      <c r="O56" t="s">
+        <v>243</v>
+      </c>
+      <c r="P56" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0005684694415437105</v>
+      </c>
+      <c r="D57">
+        <v>0.0007393357809633017</v>
+      </c>
+      <c r="E57">
+        <v>0.001527215354144573</v>
+      </c>
+      <c r="F57">
+        <v>0.002518048509955406</v>
+      </c>
+      <c r="G57">
+        <v>0.002062437124550343</v>
+      </c>
+      <c r="H57">
+        <v>1.000125164120378</v>
+      </c>
+      <c r="I57">
+        <v>0.05004387789673533</v>
+      </c>
+      <c r="J57">
+        <v>0.4841070771217346</v>
+      </c>
+      <c r="K57">
+        <v>10.25902271270752</v>
+      </c>
+      <c r="L57">
+        <v>0.08741223067045212</v>
+      </c>
+      <c r="M57">
+        <v>27.70852279663086</v>
+      </c>
+      <c r="N57" t="s">
+        <v>184</v>
+      </c>
+      <c r="O57" t="s">
+        <v>244</v>
+      </c>
+      <c r="P57" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.000761510322198465</v>
+      </c>
+      <c r="D58">
+        <v>0.0008964185835793614</v>
+      </c>
+      <c r="E58">
+        <v>0.002435842528939247</v>
+      </c>
+      <c r="F58">
+        <v>0.002176587237045169</v>
+      </c>
+      <c r="G58">
+        <v>0.001961032394319773</v>
+      </c>
+      <c r="H58">
+        <v>0.9995959401658012</v>
+      </c>
+      <c r="I58">
+        <v>0.05295930048235165</v>
+      </c>
+      <c r="J58">
+        <v>0.3680117130279541</v>
+      </c>
+      <c r="K58">
+        <v>17.83029937744141</v>
+      </c>
+      <c r="L58">
+        <v>0.1394187361001968</v>
+      </c>
+      <c r="M58">
+        <v>21.06364822387695</v>
+      </c>
+      <c r="N58" t="s">
+        <v>185</v>
+      </c>
+      <c r="O58" t="s">
+        <v>245</v>
+      </c>
+      <c r="P58" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.0009185701212199329</v>
+      </c>
+      <c r="D59">
+        <v>0.001028168480843306</v>
+      </c>
+      <c r="E59">
+        <v>0.003573467489331961</v>
+      </c>
+      <c r="F59">
+        <v>0.00195629894733429</v>
+      </c>
+      <c r="G59">
+        <v>0.001824445789679885</v>
+      </c>
+      <c r="H59">
+        <v>0.999219254428781</v>
+      </c>
+      <c r="I59">
+        <v>0.05506193299587376</v>
+      </c>
+      <c r="J59">
+        <v>0.2877229154109955</v>
+      </c>
+      <c r="K59">
+        <v>27.97946929931641</v>
+      </c>
+      <c r="L59">
+        <v>0.2045322358608246</v>
+      </c>
+      <c r="M59">
+        <v>16.46821022033691</v>
+      </c>
+      <c r="N59" t="s">
+        <v>186</v>
+      </c>
+      <c r="O59" t="s">
+        <v>246</v>
+      </c>
+      <c r="P59" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.001123495364109733</v>
+      </c>
+      <c r="D60">
+        <v>0.001113278558477759</v>
+      </c>
+      <c r="E60">
+        <v>0.005825488828122616</v>
+      </c>
+      <c r="F60">
+        <v>0.001962365349754691</v>
+      </c>
+      <c r="G60">
+        <v>0.00221529952250421</v>
+      </c>
+      <c r="H60">
+        <v>0.9995996200861561</v>
+      </c>
+      <c r="I60">
+        <v>0.06109647913628033</v>
+      </c>
+      <c r="J60">
+        <v>0.1911047399044037</v>
+      </c>
+      <c r="K60">
+        <v>37.28765487670898</v>
+      </c>
+      <c r="L60">
+        <v>0.3334297239780426</v>
+      </c>
+      <c r="M60">
+        <v>10.93813800811768</v>
+      </c>
+      <c r="N60" t="s">
+        <v>187</v>
+      </c>
+      <c r="O60" t="s">
+        <v>247</v>
+      </c>
+      <c r="P60" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.001266552764009151</v>
+      </c>
+      <c r="D61">
+        <v>0.00119486718904227</v>
+      </c>
+      <c r="E61">
+        <v>0.007587552536278963</v>
+      </c>
+      <c r="F61">
+        <v>0.002074056537821889</v>
+      </c>
+      <c r="G61">
+        <v>0.002841748530045152</v>
+      </c>
+      <c r="H61">
+        <v>1.000581395348837</v>
+      </c>
+      <c r="I61">
+        <v>0.07147264313444411</v>
+      </c>
+      <c r="J61">
+        <v>0.1574772894382477</v>
+      </c>
+      <c r="K61">
+        <v>48.99594497680664</v>
+      </c>
+      <c r="L61">
+        <v>0.4342838227748871</v>
+      </c>
+      <c r="M61">
+        <v>9.013425827026367</v>
+      </c>
+      <c r="N61" t="s">
+        <v>188</v>
+      </c>
+      <c r="O61" t="s">
+        <v>248</v>
+      </c>
+      <c r="P61" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.001062162410487202</v>
+      </c>
+      <c r="D2">
+        <v>-0.002975999610498548</v>
+      </c>
+      <c r="E2">
+        <v>0.04821500927209854</v>
+      </c>
+      <c r="F2">
+        <v>0.000739353010430932</v>
+      </c>
+      <c r="G2">
+        <v>0.000802897906396538</v>
+      </c>
+      <c r="H2">
+        <v>1.000617056728552</v>
+      </c>
+      <c r="I2">
+        <v>0.04891667749737299</v>
+      </c>
+      <c r="J2">
+        <v>-0.06172351166605949</v>
+      </c>
+      <c r="K2">
+        <v>-0.9999424815177917</v>
+      </c>
+      <c r="L2">
+        <v>2.759651184082031</v>
+      </c>
+      <c r="M2">
+        <v>-3.532828569412231</v>
+      </c>
+      <c r="N2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O2" t="s">
+        <v>369</v>
+      </c>
+      <c r="P2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.001413311213237723</v>
+      </c>
+      <c r="D3">
+        <v>-0.003466903464868665</v>
+      </c>
+      <c r="E3">
+        <v>0.0643419623374939</v>
+      </c>
+      <c r="F3">
+        <v>0.0008355954196304083</v>
+      </c>
+      <c r="G3">
+        <v>0.0008260742761194706</v>
+      </c>
+      <c r="H3">
+        <v>1.000909090024678</v>
+      </c>
+      <c r="I3">
+        <v>0.04882166581704511</v>
+      </c>
+      <c r="J3">
+        <v>-0.05388246476650238</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999885559082031</v>
+      </c>
+      <c r="L3">
+        <v>3.682699203491211</v>
+      </c>
+      <c r="M3">
+        <v>-3.084035634994507</v>
+      </c>
+      <c r="N3" t="s">
+        <v>310</v>
+      </c>
+      <c r="O3" t="s">
+        <v>370</v>
+      </c>
+      <c r="P3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.001764081638016859</v>
+      </c>
+      <c r="D4">
+        <v>-0.001451150747016072</v>
+      </c>
+      <c r="E4">
+        <v>0.04003354534506798</v>
+      </c>
+      <c r="F4">
+        <v>0.0009194481535814703</v>
+      </c>
+      <c r="G4">
+        <v>0.0008938247337937355</v>
+      </c>
+      <c r="H4">
+        <v>1.001030093413686</v>
+      </c>
+      <c r="I4">
+        <v>0.04882453734933608</v>
+      </c>
+      <c r="J4">
+        <v>-0.03624837100505829</v>
+      </c>
+      <c r="K4">
+        <v>-0.9914118051528931</v>
+      </c>
+      <c r="L4">
+        <v>2.29137396812439</v>
+      </c>
+      <c r="M4">
+        <v>-2.074724435806274</v>
+      </c>
+      <c r="N4" t="s">
+        <v>311</v>
+      </c>
+      <c r="O4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.003510125284322995</v>
+      </c>
+      <c r="D5">
+        <v>-0.002142183948308229</v>
+      </c>
+      <c r="E5">
+        <v>0.105757087469101</v>
+      </c>
+      <c r="F5">
+        <v>0.001282728975638747</v>
+      </c>
+      <c r="G5">
+        <v>0.001221068552695215</v>
+      </c>
+      <c r="H5">
+        <v>1.001109120772643</v>
+      </c>
+      <c r="I5">
+        <v>0.04891081143921311</v>
+      </c>
+      <c r="J5">
+        <v>-0.02025570161640644</v>
+      </c>
+      <c r="K5">
+        <v>-0.9991109371185303</v>
+      </c>
+      <c r="L5">
+        <v>6.053149700164795</v>
+      </c>
+      <c r="M5">
+        <v>-1.159362435340881</v>
+      </c>
+      <c r="N5" t="s">
+        <v>312</v>
+      </c>
+      <c r="O5" t="s">
+        <v>372</v>
+      </c>
+      <c r="P5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.006965125704437437</v>
+      </c>
+      <c r="D6">
+        <v>0.003628430655226111</v>
+      </c>
+      <c r="E6">
+        <v>0.0235197301954031</v>
+      </c>
+      <c r="F6">
+        <v>0.001769101712852716</v>
+      </c>
+      <c r="G6">
+        <v>0.0015184081858024</v>
+      </c>
+      <c r="H6">
+        <v>1.001056500874591</v>
+      </c>
+      <c r="I6">
+        <v>0.04913270536690479</v>
+      </c>
+      <c r="J6">
+        <v>0.1542717814445496</v>
+      </c>
+      <c r="K6">
+        <v>142205.859375</v>
+      </c>
+      <c r="L6">
+        <v>1.34618353843689</v>
+      </c>
+      <c r="M6">
+        <v>8.829954147338867</v>
+      </c>
+      <c r="N6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O6" t="s">
+        <v>373</v>
+      </c>
+      <c r="P6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01380583781374876</v>
+      </c>
+      <c r="D7">
+        <v>0.007364713586866856</v>
+      </c>
+      <c r="E7">
+        <v>0.04468784108757973</v>
+      </c>
+      <c r="F7">
+        <v>0.002157217124477029</v>
+      </c>
+      <c r="G7">
+        <v>0.001766686677001417</v>
+      </c>
+      <c r="H7">
+        <v>1.000853724368888</v>
+      </c>
+      <c r="I7">
+        <v>0.04934127212229312</v>
+      </c>
+      <c r="J7">
+        <v>0.1648035198450089</v>
+      </c>
+      <c r="K7">
+        <v>27529119744</v>
+      </c>
+      <c r="L7">
+        <v>2.557769060134888</v>
+      </c>
+      <c r="M7">
+        <v>9.432751655578613</v>
+      </c>
+      <c r="N7" t="s">
+        <v>314</v>
+      </c>
+      <c r="O7" t="s">
+        <v>374</v>
+      </c>
+      <c r="P7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.03407104623732774</v>
+      </c>
+      <c r="D8">
+        <v>0.01910126209259033</v>
+      </c>
+      <c r="E8">
+        <v>0.1312412619590759</v>
+      </c>
+      <c r="F8">
+        <v>0.002419998636469245</v>
+      </c>
+      <c r="G8">
+        <v>0.002038529608398676</v>
+      </c>
+      <c r="H8">
+        <v>1.000413379967411</v>
+      </c>
+      <c r="I8">
+        <v>0.05115688545608872</v>
+      </c>
+      <c r="J8">
+        <v>0.1455431133508682</v>
+      </c>
+      <c r="K8">
+        <v>8.317714379160746E+26</v>
+      </c>
+      <c r="L8">
+        <v>7.511770725250244</v>
+      </c>
+      <c r="M8">
+        <v>8.330356597900391</v>
+      </c>
+      <c r="N8" t="s">
+        <v>315</v>
+      </c>
+      <c r="O8" t="s">
+        <v>375</v>
+      </c>
+      <c r="P8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.06768185724057735</v>
+      </c>
+      <c r="D9">
+        <v>0.0370597243309021</v>
+      </c>
+      <c r="E9">
+        <v>0.2410728186368942</v>
+      </c>
+      <c r="F9">
+        <v>0.002299298532307148</v>
+      </c>
+      <c r="G9">
+        <v>0.00194921251386404</v>
+      </c>
+      <c r="H9">
+        <v>0.9999554255140624</v>
+      </c>
+      <c r="I9">
+        <v>0.05322845687053821</v>
+      </c>
+      <c r="J9">
+        <v>0.1537283360958099</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>13.79812812805176</v>
+      </c>
+      <c r="M9">
+        <v>8.798849105834961</v>
+      </c>
+      <c r="N9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O9" t="s">
+        <v>376</v>
+      </c>
+      <c r="P9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.1690864165890834</v>
+      </c>
+      <c r="D10">
+        <v>0.09346775710582733</v>
+      </c>
+      <c r="E10">
+        <v>0.6354187726974487</v>
+      </c>
+      <c r="F10">
+        <v>0.002108827000483871</v>
+      </c>
+      <c r="G10">
+        <v>0.001909253653138876</v>
+      </c>
+      <c r="H10">
+        <v>1.000823610294235</v>
+      </c>
+      <c r="I10">
+        <v>0.05839376985735346</v>
+      </c>
+      <c r="J10">
+        <v>0.1470963060855865</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>36.36905288696289</v>
+      </c>
+      <c r="M10">
+        <v>8.419256210327148</v>
+      </c>
+      <c r="N10" t="s">
+        <v>317</v>
+      </c>
+      <c r="O10" t="s">
+        <v>377</v>
+      </c>
+      <c r="P10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.3310436475050791</v>
+      </c>
+      <c r="D11">
+        <v>0.1812683343887329</v>
+      </c>
+      <c r="E11">
+        <v>1.177192091941833</v>
+      </c>
+      <c r="F11">
+        <v>0.002031018026173115</v>
+      </c>
+      <c r="G11">
+        <v>0.00208766246214509</v>
+      </c>
+      <c r="H11">
+        <v>1.002050183598531</v>
+      </c>
+      <c r="I11">
+        <v>0.06753264005703871</v>
+      </c>
+      <c r="J11">
+        <v>0.1539836525917053</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>67.37818145751953</v>
+      </c>
+      <c r="M11">
+        <v>8.813462257385254</v>
+      </c>
+      <c r="N11" t="s">
+        <v>318</v>
+      </c>
+      <c r="O11" t="s">
+        <v>378</v>
+      </c>
+      <c r="P11" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.001336383110336451</v>
+      </c>
+      <c r="D12">
+        <v>-0.0003305485588498414</v>
+      </c>
+      <c r="E12">
+        <v>0.01142188999801874</v>
+      </c>
+      <c r="F12">
+        <v>0.0007448328542523086</v>
+      </c>
+      <c r="G12">
+        <v>0.0008007781580090523</v>
+      </c>
+      <c r="H12">
+        <v>1.000561510268466</v>
+      </c>
+      <c r="I12">
+        <v>0.04894168202362802</v>
+      </c>
+      <c r="J12">
+        <v>-0.02893991768360138</v>
+      </c>
+      <c r="K12">
+        <v>-0.6614615917205811</v>
+      </c>
+      <c r="L12">
+        <v>0.6537473201751709</v>
+      </c>
+      <c r="M12">
+        <v>-1.656415343284607</v>
+      </c>
+      <c r="N12" t="s">
+        <v>319</v>
+      </c>
+      <c r="O12" t="s">
+        <v>379</v>
+      </c>
+      <c r="P12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.001779206876008313</v>
+      </c>
+      <c r="D13">
+        <v>0.0001457789185224101</v>
+      </c>
+      <c r="E13">
+        <v>0.01373726688325405</v>
+      </c>
+      <c r="F13">
+        <v>0.0008512856438755989</v>
+      </c>
+      <c r="G13">
+        <v>0.0008339941268786788</v>
+      </c>
+      <c r="H13">
+        <v>1.000857732975862</v>
+      </c>
+      <c r="I13">
+        <v>0.0488626537633543</v>
+      </c>
+      <c r="J13">
+        <v>0.01061192993074656</v>
+      </c>
+      <c r="K13">
+        <v>0.6121729612350464</v>
+      </c>
+      <c r="L13">
+        <v>0.7862710356712341</v>
+      </c>
+      <c r="M13">
+        <v>0.6073881387710571</v>
+      </c>
+      <c r="N13" t="s">
+        <v>320</v>
+      </c>
+      <c r="O13" t="s">
+        <v>380</v>
+      </c>
+      <c r="P13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.00222082302852718</v>
+      </c>
+      <c r="D14">
+        <v>0.0007670597406104207</v>
+      </c>
+      <c r="E14">
+        <v>0.01680115796625614</v>
+      </c>
+      <c r="F14">
+        <v>0.0009367692400701344</v>
+      </c>
+      <c r="G14">
+        <v>0.000910271774046123</v>
+      </c>
+      <c r="H14">
+        <v>1.000974928617014</v>
+      </c>
+      <c r="I14">
+        <v>0.048885642997077</v>
+      </c>
+      <c r="J14">
+        <v>0.04565517231822014</v>
+      </c>
+      <c r="K14">
+        <v>11.33073329925537</v>
+      </c>
+      <c r="L14">
+        <v>0.9616369605064392</v>
+      </c>
+      <c r="M14">
+        <v>2.613135576248169</v>
+      </c>
+      <c r="N14" t="s">
+        <v>321</v>
+      </c>
+      <c r="O14" t="s">
+        <v>381</v>
+      </c>
+      <c r="P14" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.004423193851927136</v>
+      </c>
+      <c r="D15">
+        <v>0.002439436735585332</v>
+      </c>
+      <c r="E15">
+        <v>0.02801618725061417</v>
+      </c>
+      <c r="F15">
+        <v>0.001328171580098569</v>
+      </c>
+      <c r="G15">
+        <v>0.001261536846868694</v>
+      </c>
+      <c r="H15">
+        <v>1.001043924305256</v>
+      </c>
+      <c r="I15">
+        <v>0.04896384024237013</v>
+      </c>
+      <c r="J15">
+        <v>0.08707240223884583</v>
+      </c>
+      <c r="K15">
+        <v>2925.834228515625</v>
+      </c>
+      <c r="L15">
+        <v>1.603544354438782</v>
+      </c>
+      <c r="M15">
+        <v>4.983706474304199</v>
+      </c>
+      <c r="N15" t="s">
+        <v>322</v>
+      </c>
+      <c r="O15" t="s">
+        <v>382</v>
+      </c>
+      <c r="P15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.008784693592591581</v>
+      </c>
+      <c r="D16">
+        <v>0.004967274609953165</v>
+      </c>
+      <c r="E16">
+        <v>0.04100247845053673</v>
+      </c>
+      <c r="F16">
+        <v>0.001822104095481336</v>
+      </c>
+      <c r="G16">
+        <v>0.001554654212668538</v>
+      </c>
+      <c r="H16">
+        <v>1.001023693631871</v>
+      </c>
+      <c r="I16">
+        <v>0.0491698208692697</v>
+      </c>
+      <c r="J16">
+        <v>0.1211457177996635</v>
+      </c>
+      <c r="K16">
+        <v>11214250</v>
+      </c>
+      <c r="L16">
+        <v>2.346832275390625</v>
+      </c>
+      <c r="M16">
+        <v>6.933938980102539</v>
+      </c>
+      <c r="N16" t="s">
+        <v>323</v>
+      </c>
+      <c r="O16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P16" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.01740246043305797</v>
+      </c>
+      <c r="D17">
+        <v>0.0097334124147892</v>
+      </c>
+      <c r="E17">
+        <v>0.07905548065900803</v>
+      </c>
+      <c r="F17">
+        <v>0.002239188179373741</v>
+      </c>
+      <c r="G17">
+        <v>0.001801143400371075</v>
+      </c>
+      <c r="H17">
+        <v>1.000822820739729</v>
+      </c>
+      <c r="I17">
+        <v>0.04934856602066957</v>
+      </c>
+      <c r="J17">
+        <v>0.1231212839484215</v>
+      </c>
+      <c r="K17">
+        <v>60433239113728</v>
+      </c>
+      <c r="L17">
+        <v>4.524847030639648</v>
+      </c>
+      <c r="M17">
+        <v>7.047012805938721</v>
+      </c>
+      <c r="N17" t="s">
+        <v>324</v>
+      </c>
+      <c r="O17" t="s">
+        <v>384</v>
+      </c>
+      <c r="P17" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.04312720808625174</v>
+      </c>
+      <c r="D18">
+        <v>0.02392782457172871</v>
+      </c>
+      <c r="E18">
+        <v>0.1966410875320435</v>
+      </c>
+      <c r="F18">
+        <v>0.00243665324524045</v>
+      </c>
+      <c r="G18">
+        <v>0.002039456041529775</v>
+      </c>
+      <c r="H18">
+        <v>1.000382244010561</v>
+      </c>
+      <c r="I18">
+        <v>0.05114890890800201</v>
+      </c>
+      <c r="J18">
+        <v>0.121682733297348</v>
+      </c>
+      <c r="K18">
+        <v>4.388846228872742E+33</v>
+      </c>
+      <c r="L18">
+        <v>11.25501823425293</v>
+      </c>
+      <c r="M18">
+        <v>6.964675426483154</v>
+      </c>
+      <c r="N18" t="s">
+        <v>325</v>
+      </c>
+      <c r="O18" t="s">
+        <v>385</v>
+      </c>
+      <c r="P18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.0851011806592883</v>
+      </c>
+      <c r="D19">
+        <v>0.04909186065196991</v>
+      </c>
+      <c r="E19">
+        <v>0.43683722615242</v>
+      </c>
+      <c r="F19">
+        <v>0.002288317540660501</v>
+      </c>
+      <c r="G19">
+        <v>0.001912658102810383</v>
+      </c>
+      <c r="H19">
+        <v>0.9998956831348585</v>
+      </c>
+      <c r="I19">
+        <v>0.05328389567831149</v>
+      </c>
+      <c r="J19">
+        <v>0.112380214035511</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>25.00296974182129</v>
+      </c>
+      <c r="M19">
+        <v>6.432233333587646</v>
+      </c>
+      <c r="N19" t="s">
+        <v>326</v>
+      </c>
+      <c r="O19" t="s">
+        <v>386</v>
+      </c>
+      <c r="P19" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.21361017093382</v>
+      </c>
+      <c r="D20">
+        <v>0.1229842007160187</v>
+      </c>
+      <c r="E20">
+        <v>1.101213574409485</v>
+      </c>
+      <c r="F20">
+        <v>0.002089429413899779</v>
+      </c>
+      <c r="G20">
+        <v>0.001919934409670532</v>
+      </c>
+      <c r="H20">
+        <v>1.000687611382226</v>
+      </c>
+      <c r="I20">
+        <v>0.05884718697272701</v>
+      </c>
+      <c r="J20">
+        <v>0.1116806045174599</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>63.02944564819336</v>
+      </c>
+      <c r="M20">
+        <v>6.392190456390381</v>
+      </c>
+      <c r="N20" t="s">
+        <v>327</v>
+      </c>
+      <c r="O20" t="s">
+        <v>387</v>
+      </c>
+      <c r="P20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.4135124231942781</v>
+      </c>
+      <c r="D21">
+        <v>0.2353901416063309</v>
+      </c>
+      <c r="E21">
+        <v>1.971038818359375</v>
+      </c>
+      <c r="F21">
+        <v>0.002013880060985684</v>
+      </c>
+      <c r="G21">
+        <v>0.002015286590903997</v>
+      </c>
+      <c r="H21">
+        <v>1.002050183598531</v>
+      </c>
+      <c r="I21">
+        <v>0.06753264005703871</v>
+      </c>
+      <c r="J21">
+        <v>0.1194244101643562</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>112.815071105957</v>
+      </c>
+      <c r="M21">
+        <v>6.8354172706604</v>
+      </c>
+      <c r="N21" t="s">
+        <v>328</v>
+      </c>
+      <c r="O21" t="s">
+        <v>388</v>
+      </c>
+      <c r="P21" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0007320410360261568</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003992080164607614</v>
+      </c>
+      <c r="E22">
+        <v>0.003132824553176761</v>
+      </c>
+      <c r="F22">
+        <v>0.0007554455660283566</v>
+      </c>
+      <c r="G22">
+        <v>0.0007991593447513878</v>
+      </c>
+      <c r="H22">
+        <v>1.000540643606573</v>
+      </c>
+      <c r="I22">
+        <v>0.04892907410242631</v>
+      </c>
+      <c r="J22">
+        <v>-0.1274275034666061</v>
+      </c>
+      <c r="K22">
+        <v>-0.7296789288520813</v>
+      </c>
+      <c r="L22">
+        <v>0.1793114393949509</v>
+      </c>
+      <c r="M22">
+        <v>-7.293485164642334</v>
+      </c>
+      <c r="N22" t="s">
+        <v>329</v>
+      </c>
+      <c r="O22" t="s">
+        <v>389</v>
+      </c>
+      <c r="P22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.0009734290848123041</v>
+      </c>
+      <c r="D23">
+        <v>-0.0001130495074903592</v>
+      </c>
+      <c r="E23">
+        <v>0.00408813776448369</v>
+      </c>
+      <c r="F23">
+        <v>0.0008582661976106465</v>
+      </c>
+      <c r="G23">
+        <v>0.0008492596098221838</v>
+      </c>
+      <c r="H23">
+        <v>1.000805046696785</v>
+      </c>
+      <c r="I23">
+        <v>0.04886733234768677</v>
+      </c>
+      <c r="J23">
+        <v>-0.02765305712819099</v>
+      </c>
+      <c r="K23">
+        <v>-0.3095683455467224</v>
+      </c>
+      <c r="L23">
+        <v>0.2339900881052017</v>
+      </c>
+      <c r="M23">
+        <v>-1.582760095596313</v>
+      </c>
+      <c r="N23" t="s">
+        <v>330</v>
+      </c>
+      <c r="O23" t="s">
+        <v>390</v>
+      </c>
+      <c r="P23" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.001213753447933424</v>
+      </c>
+      <c r="D24">
+        <v>0.0001105071496567689</v>
+      </c>
+      <c r="E24">
+        <v>0.005095081403851509</v>
+      </c>
+      <c r="F24">
+        <v>0.0009554402204230428</v>
+      </c>
+      <c r="G24">
+        <v>0.000938094686716795</v>
+      </c>
+      <c r="H24">
+        <v>1.000918158569987</v>
+      </c>
+      <c r="I24">
+        <v>0.04888023353116885</v>
+      </c>
+      <c r="J24">
+        <v>0.02168898656964302</v>
+      </c>
+      <c r="K24">
+        <v>0.4362003803253174</v>
+      </c>
+      <c r="L24">
+        <v>0.2916238605976105</v>
+      </c>
+      <c r="M24">
+        <v>1.241398453712463</v>
+      </c>
+      <c r="N24" t="s">
+        <v>331</v>
+      </c>
+      <c r="O24" t="s">
+        <v>391</v>
+      </c>
+      <c r="P24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.00240356812707632</v>
+      </c>
+      <c r="D25">
+        <v>0.001079507172107697</v>
+      </c>
+      <c r="E25">
+        <v>0.00936465710401535</v>
+      </c>
+      <c r="F25">
+        <v>0.001394699676893651</v>
+      </c>
+      <c r="G25">
+        <v>0.001298150164075196</v>
+      </c>
+      <c r="H25">
+        <v>1.000994153228843</v>
+      </c>
+      <c r="I25">
+        <v>0.04897092286446198</v>
+      </c>
+      <c r="J25">
+        <v>0.1152746081352234</v>
+      </c>
+      <c r="K25">
+        <v>33.28571319580078</v>
+      </c>
+      <c r="L25">
+        <v>0.5359988212585449</v>
+      </c>
+      <c r="M25">
+        <v>6.597898006439209</v>
+      </c>
+      <c r="N25" t="s">
+        <v>332</v>
+      </c>
+      <c r="O25" t="s">
+        <v>392</v>
+      </c>
+      <c r="P25" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.004734624345347702</v>
+      </c>
+      <c r="D26">
+        <v>0.002403983846306801</v>
+      </c>
+      <c r="E26">
+        <v>0.01835317723453045</v>
+      </c>
+      <c r="F26">
+        <v>0.001899975701235235</v>
+      </c>
+      <c r="G26">
+        <v>0.001602903008460999</v>
+      </c>
+      <c r="H26">
+        <v>1.001027427076716</v>
+      </c>
+      <c r="I26">
+        <v>0.04916557780678888</v>
+      </c>
+      <c r="J26">
+        <v>0.1309846192598343</v>
+      </c>
+      <c r="K26">
+        <v>2606.036865234375</v>
+      </c>
+      <c r="L26">
+        <v>1.050468921661377</v>
+      </c>
+      <c r="M26">
+        <v>7.497081756591797</v>
+      </c>
+      <c r="N26" t="s">
+        <v>333</v>
+      </c>
+      <c r="O26" t="s">
+        <v>393</v>
+      </c>
+      <c r="P26" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.009307116351841687</v>
+      </c>
+      <c r="D27">
+        <v>0.005000406876206398</v>
+      </c>
+      <c r="E27">
+        <v>0.03449722006917</v>
+      </c>
+      <c r="F27">
+        <v>0.002322788117453456</v>
+      </c>
+      <c r="G27">
+        <v>0.001865355181507766</v>
+      </c>
+      <c r="H27">
+        <v>1.000748086217863</v>
+      </c>
+      <c r="I27">
+        <v>0.04940938395694805</v>
+      </c>
+      <c r="J27">
+        <v>0.1449510157108307</v>
+      </c>
+      <c r="K27">
+        <v>12488717</v>
+      </c>
+      <c r="L27">
+        <v>1.974495053291321</v>
+      </c>
+      <c r="M27">
+        <v>8.296466827392578</v>
+      </c>
+      <c r="N27" t="s">
+        <v>334</v>
+      </c>
+      <c r="O27" t="s">
+        <v>394</v>
+      </c>
+      <c r="P27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.02280206727014141</v>
+      </c>
+      <c r="D28">
+        <v>0.01201379578560591</v>
+      </c>
+      <c r="E28">
+        <v>0.08338558673858643</v>
+      </c>
+      <c r="F28">
+        <v>0.002455709502100945</v>
+      </c>
+      <c r="G28">
+        <v>0.00205265125259757</v>
+      </c>
+      <c r="H28">
+        <v>1.000368744682277</v>
+      </c>
+      <c r="I28">
+        <v>0.05121823011197615</v>
+      </c>
+      <c r="J28">
+        <v>0.1440752148628235</v>
+      </c>
+      <c r="K28">
+        <v>9.789265554702336E+16</v>
+      </c>
+      <c r="L28">
+        <v>4.77268648147583</v>
+      </c>
+      <c r="M28">
+        <v>8.246339797973633</v>
+      </c>
+      <c r="N28" t="s">
+        <v>335</v>
+      </c>
+      <c r="O28" t="s">
+        <v>395</v>
+      </c>
+      <c r="P28" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.04534898337585563</v>
+      </c>
+      <c r="D29">
+        <v>0.02397209405899048</v>
+      </c>
+      <c r="E29">
+        <v>0.1747871339321136</v>
+      </c>
+      <c r="F29">
+        <v>0.002254145918413997</v>
+      </c>
+      <c r="G29">
+        <v>0.001890743151307106</v>
+      </c>
+      <c r="H29">
+        <v>0.9999807928435912</v>
+      </c>
+      <c r="I29">
+        <v>0.05318358775775955</v>
+      </c>
+      <c r="J29">
+        <v>0.1371502280235291</v>
+      </c>
+      <c r="K29">
+        <v>5.055941167542651E+33</v>
+      </c>
+      <c r="L29">
+        <v>10.00417804718018</v>
+      </c>
+      <c r="M29">
+        <v>7.849978446960449</v>
+      </c>
+      <c r="N29" t="s">
+        <v>336</v>
+      </c>
+      <c r="O29" t="s">
+        <v>396</v>
+      </c>
+      <c r="P29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.111300306377309</v>
+      </c>
+      <c r="D30">
+        <v>0.05937178060412407</v>
+      </c>
+      <c r="E30">
+        <v>0.4505092203617096</v>
+      </c>
+      <c r="F30">
+        <v>0.00205325847491622</v>
+      </c>
+      <c r="G30">
+        <v>0.001897424110211432</v>
+      </c>
+      <c r="H30">
+        <v>1.000687611382226</v>
+      </c>
+      <c r="I30">
+        <v>0.05884718697272701</v>
+      </c>
+      <c r="J30">
+        <v>0.1317881643772125</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>25.78550338745117</v>
+      </c>
+      <c r="M30">
+        <v>7.543073654174805</v>
+      </c>
+      <c r="N30" t="s">
+        <v>337</v>
+      </c>
+      <c r="O30" t="s">
+        <v>397</v>
+      </c>
+      <c r="P30" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.2270231641361245</v>
+      </c>
+      <c r="D31">
+        <v>0.1237619146704674</v>
+      </c>
+      <c r="E31">
+        <v>0.9766779541969299</v>
+      </c>
+      <c r="F31">
+        <v>0.002012478653341532</v>
+      </c>
+      <c r="G31">
+        <v>0.00206028763204813</v>
+      </c>
+      <c r="H31">
+        <v>1.001774785801714</v>
+      </c>
+      <c r="I31">
+        <v>0.06859257480808534</v>
+      </c>
+      <c r="J31">
+        <v>0.1267172247171402</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>55.90148162841797</v>
+      </c>
+      <c r="M31">
+        <v>7.25283145904541</v>
+      </c>
+      <c r="N31" t="s">
+        <v>338</v>
+      </c>
+      <c r="O31" t="s">
+        <v>398</v>
+      </c>
+      <c r="P31" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.000511678032211543</v>
+      </c>
+      <c r="D32">
+        <v>-0.0001314335968345404</v>
+      </c>
+      <c r="E32">
+        <v>0.003230034839361906</v>
+      </c>
+      <c r="F32">
+        <v>0.0007511021685786545</v>
+      </c>
+      <c r="G32">
+        <v>0.000794431718531996</v>
+      </c>
+      <c r="H32">
+        <v>1.00050735018517</v>
+      </c>
+      <c r="I32">
+        <v>0.04895599102634619</v>
+      </c>
+      <c r="J32">
+        <v>-0.040691077709198</v>
+      </c>
+      <c r="K32">
+        <v>-0.3498727679252625</v>
+      </c>
+      <c r="L32">
+        <v>0.184875413775444</v>
+      </c>
+      <c r="M32">
+        <v>-2.329008817672729</v>
+      </c>
+      <c r="N32" t="s">
+        <v>339</v>
+      </c>
+      <c r="O32" t="s">
+        <v>399</v>
+      </c>
+      <c r="P32" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0006793904201931265</v>
+      </c>
+      <c r="D33">
+        <v>9.960044553736225E-05</v>
+      </c>
+      <c r="E33">
+        <v>0.004217911045998335</v>
+      </c>
+      <c r="F33">
+        <v>0.0008714497671462595</v>
+      </c>
+      <c r="G33">
+        <v>0.0008607374038547277</v>
+      </c>
+      <c r="H33">
+        <v>1.000708639734545</v>
+      </c>
+      <c r="I33">
+        <v>0.04889393145851587</v>
+      </c>
+      <c r="J33">
+        <v>0.02361368946731091</v>
+      </c>
+      <c r="K33">
+        <v>0.3860617876052856</v>
+      </c>
+      <c r="L33">
+        <v>0.2414178401231766</v>
+      </c>
+      <c r="M33">
+        <v>1.351561427116394</v>
+      </c>
+      <c r="N33" t="s">
+        <v>340</v>
+      </c>
+      <c r="O33" t="s">
+        <v>400</v>
+      </c>
+      <c r="P33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.0008458040015500661</v>
+      </c>
+      <c r="D34">
+        <v>0.0002911399060394615</v>
+      </c>
+      <c r="E34">
+        <v>0.005274136550724506</v>
+      </c>
+      <c r="F34">
+        <v>0.0009905281476676464</v>
+      </c>
+      <c r="G34">
+        <v>0.0009646423859521747</v>
+      </c>
+      <c r="H34">
+        <v>1.000816045775252</v>
+      </c>
+      <c r="I34">
+        <v>0.04892154562221487</v>
+      </c>
+      <c r="J34">
+        <v>0.05520143359899521</v>
+      </c>
+      <c r="K34">
+        <v>1.594865322113037</v>
+      </c>
+      <c r="L34">
+        <v>0.3018723428249359</v>
+      </c>
+      <c r="M34">
+        <v>3.159528732299805</v>
+      </c>
+      <c r="N34" t="s">
+        <v>341</v>
+      </c>
+      <c r="O34" t="s">
+        <v>401</v>
+      </c>
+      <c r="P34" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.001662573334156376</v>
+      </c>
+      <c r="D35">
+        <v>0.0009316115756519139</v>
+      </c>
+      <c r="E35">
+        <v>0.009985123760998249</v>
+      </c>
+      <c r="F35">
+        <v>0.001472148112952709</v>
+      </c>
+      <c r="G35">
+        <v>0.001319864764809608</v>
+      </c>
+      <c r="H35">
+        <v>1.000890525808237</v>
+      </c>
+      <c r="I35">
+        <v>0.04897981064870026</v>
+      </c>
+      <c r="J35">
+        <v>0.09329995512962341</v>
+      </c>
+      <c r="K35">
+        <v>20.12734794616699</v>
+      </c>
+      <c r="L35">
+        <v>0.5715120434761047</v>
+      </c>
+      <c r="M35">
+        <v>5.34014892578125</v>
+      </c>
+      <c r="N35" t="s">
+        <v>342</v>
+      </c>
+      <c r="O35" t="s">
+        <v>402</v>
+      </c>
+      <c r="P35" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.003240511097821571</v>
+      </c>
+      <c r="D36">
+        <v>0.002049712231382728</v>
+      </c>
+      <c r="E36">
+        <v>0.01990874111652374</v>
+      </c>
+      <c r="F36">
+        <v>0.002001260640099645</v>
+      </c>
+      <c r="G36">
+        <v>0.001665374031290412</v>
+      </c>
+      <c r="H36">
+        <v>1.000948409487252</v>
+      </c>
+      <c r="I36">
+        <v>0.04922107115017634</v>
+      </c>
+      <c r="J36">
+        <v>0.1029553934931755</v>
+      </c>
+      <c r="K36">
+        <v>817.8446044921875</v>
+      </c>
+      <c r="L36">
+        <v>1.139503717422485</v>
+      </c>
+      <c r="M36">
+        <v>5.892791271209717</v>
+      </c>
+      <c r="N36" t="s">
+        <v>343</v>
+      </c>
+      <c r="O36" t="s">
+        <v>403</v>
+      </c>
+      <c r="P36" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.006290300676466138</v>
+      </c>
+      <c r="D37">
+        <v>0.003902448108419776</v>
+      </c>
+      <c r="E37">
+        <v>0.03778900951147079</v>
+      </c>
+      <c r="F37">
+        <v>0.002422707388177514</v>
+      </c>
+      <c r="G37">
+        <v>0.001954043749719858</v>
+      </c>
+      <c r="H37">
+        <v>1.000718171938867</v>
+      </c>
+      <c r="I37">
+        <v>0.04938277369655785</v>
+      </c>
+      <c r="J37">
+        <v>0.1032693907618523</v>
+      </c>
+      <c r="K37">
+        <v>347838.90625</v>
+      </c>
+      <c r="L37">
+        <v>2.162904977798462</v>
+      </c>
+      <c r="M37">
+        <v>5.910763263702393</v>
+      </c>
+      <c r="N37" t="s">
+        <v>344</v>
+      </c>
+      <c r="O37" t="s">
+        <v>404</v>
+      </c>
+      <c r="P37" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.01524218252069142</v>
+      </c>
+      <c r="D38">
+        <v>0.009036165662109852</v>
+      </c>
+      <c r="E38">
+        <v>0.08844592422246933</v>
+      </c>
+      <c r="F38">
+        <v>0.002470447914674878</v>
+      </c>
+      <c r="G38">
+        <v>0.002043021144345403</v>
+      </c>
+      <c r="H38">
+        <v>1.000413704562405</v>
+      </c>
+      <c r="I38">
+        <v>0.05123588922525264</v>
+      </c>
+      <c r="J38">
+        <v>0.1021659895777702</v>
+      </c>
+      <c r="K38">
+        <v>6287533801472</v>
+      </c>
+      <c r="L38">
+        <v>5.06232213973999</v>
+      </c>
+      <c r="M38">
+        <v>5.84760856628418</v>
+      </c>
+      <c r="N38" t="s">
+        <v>345</v>
+      </c>
+      <c r="O38" t="s">
+        <v>405</v>
+      </c>
+      <c r="P38" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.03000966618972718</v>
+      </c>
+      <c r="D39">
+        <v>0.01748601347208023</v>
+      </c>
+      <c r="E39">
+        <v>0.1741209477186203</v>
+      </c>
+      <c r="F39">
+        <v>0.002218782203271985</v>
+      </c>
+      <c r="G39">
+        <v>0.001893087523058057</v>
+      </c>
+      <c r="H39">
+        <v>0.9998676440141688</v>
+      </c>
+      <c r="I39">
+        <v>0.0535368727555561</v>
+      </c>
+      <c r="J39">
+        <v>0.1004245281219482</v>
+      </c>
+      <c r="K39">
+        <v>4.604089418633533E+24</v>
+      </c>
+      <c r="L39">
+        <v>9.966047286987305</v>
+      </c>
+      <c r="M39">
+        <v>5.747933387756348</v>
+      </c>
+      <c r="N39" t="s">
+        <v>346</v>
+      </c>
+      <c r="O39" t="s">
+        <v>406</v>
+      </c>
+      <c r="P39" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.07308944749108921</v>
+      </c>
+      <c r="D40">
+        <v>0.04316211491823196</v>
+      </c>
+      <c r="E40">
+        <v>0.4394778311252594</v>
+      </c>
+      <c r="F40">
+        <v>0.002012290293350816</v>
+      </c>
+      <c r="G40">
+        <v>0.001883454038761556</v>
+      </c>
+      <c r="H40">
+        <v>1.000619611926221</v>
+      </c>
+      <c r="I40">
+        <v>0.05894427491670855</v>
+      </c>
+      <c r="J40">
+        <v>0.09821227192878723</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>25.15410804748535</v>
+      </c>
+      <c r="M40">
+        <v>5.621312141418457</v>
+      </c>
+      <c r="N40" t="s">
+        <v>347</v>
+      </c>
+      <c r="O40" t="s">
+        <v>407</v>
+      </c>
+      <c r="P40" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.150459004881752</v>
+      </c>
+      <c r="D41">
+        <v>0.09085406363010406</v>
+      </c>
+      <c r="E41">
+        <v>1.009888768196106</v>
+      </c>
+      <c r="F41">
+        <v>0.001999716507270932</v>
+      </c>
+      <c r="G41">
+        <v>0.002153560519218445</v>
+      </c>
+      <c r="H41">
+        <v>1.001376988984088</v>
+      </c>
+      <c r="I41">
+        <v>0.06970378012990126</v>
+      </c>
+      <c r="J41">
+        <v>0.08996442705392838</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>57.80234909057617</v>
+      </c>
+      <c r="M41">
+        <v>5.149235725402832</v>
+      </c>
+      <c r="N41" t="s">
+        <v>348</v>
+      </c>
+      <c r="O41" t="s">
+        <v>408</v>
+      </c>
+      <c r="P41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.0005546659063405239</v>
+      </c>
+      <c r="D42">
+        <v>-0.0001730789517750964</v>
+      </c>
+      <c r="E42">
+        <v>0.003431241028010845</v>
+      </c>
+      <c r="F42">
+        <v>0.0007685260497964919</v>
+      </c>
+      <c r="G42">
+        <v>0.0008052506018429995</v>
+      </c>
+      <c r="H42">
+        <v>1.0003624587491</v>
+      </c>
+      <c r="I42">
+        <v>0.0490208602244026</v>
+      </c>
+      <c r="J42">
+        <v>-0.05044208467006683</v>
+      </c>
+      <c r="K42">
+        <v>-0.4328311085700989</v>
+      </c>
+      <c r="L42">
+        <v>0.1963917165994644</v>
+      </c>
+      <c r="M42">
+        <v>-2.887120962142944</v>
+      </c>
+      <c r="N42" t="s">
+        <v>349</v>
+      </c>
+      <c r="O42" t="s">
+        <v>409</v>
+      </c>
+      <c r="P42" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.0007360057816777017</v>
+      </c>
+      <c r="D43">
+        <v>-0.000111019988253247</v>
+      </c>
+      <c r="E43">
+        <v>0.004882026929408312</v>
+      </c>
+      <c r="F43">
+        <v>0.0009189830161631107</v>
+      </c>
+      <c r="G43">
+        <v>0.0009152947459369898</v>
+      </c>
+      <c r="H43">
+        <v>1.000538765085578</v>
+      </c>
+      <c r="I43">
+        <v>0.04893507833054063</v>
+      </c>
+      <c r="J43">
+        <v>-0.0227405522018671</v>
+      </c>
+      <c r="K43">
+        <v>-0.3049688339233398</v>
+      </c>
+      <c r="L43">
+        <v>0.2794294059276581</v>
+      </c>
+      <c r="M43">
+        <v>-1.301586270332336</v>
+      </c>
+      <c r="N43" t="s">
+        <v>350</v>
+      </c>
+      <c r="O43" t="s">
+        <v>410</v>
+      </c>
+      <c r="P43" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0009153508388950148</v>
+      </c>
+      <c r="D44">
+        <v>-6.515486165881157E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.006011151243001223</v>
+      </c>
+      <c r="F44">
+        <v>0.001056026900187135</v>
+      </c>
+      <c r="G44">
+        <v>0.001037669484503567</v>
+      </c>
+      <c r="H44">
+        <v>1.000610380722709</v>
+      </c>
+      <c r="I44">
+        <v>0.04897317103807052</v>
+      </c>
+      <c r="J44">
+        <v>-0.01083899848163128</v>
+      </c>
+      <c r="K44">
+        <v>-0.1921924352645874</v>
+      </c>
+      <c r="L44">
+        <v>0.3440563678741455</v>
+      </c>
+      <c r="M44">
+        <v>-0.620384693145752</v>
+      </c>
+      <c r="N44" t="s">
+        <v>351</v>
+      </c>
+      <c r="O44" t="s">
+        <v>411</v>
+      </c>
+      <c r="P44" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.001790228628047484</v>
+      </c>
+      <c r="D45">
+        <v>8.332984725711867E-05</v>
+      </c>
+      <c r="E45">
+        <v>0.01163552887737751</v>
+      </c>
+      <c r="F45">
+        <v>0.001591106527484953</v>
+      </c>
+      <c r="G45">
+        <v>0.001390435732901096</v>
+      </c>
+      <c r="H45">
+        <v>1.000754555426994</v>
+      </c>
+      <c r="I45">
+        <v>0.04905519807739423</v>
+      </c>
+      <c r="J45">
+        <v>0.007161672692745924</v>
+      </c>
+      <c r="K45">
+        <v>0.3138593435287476</v>
+      </c>
+      <c r="L45">
+        <v>0.6659752130508423</v>
+      </c>
+      <c r="M45">
+        <v>0.4099080264568329</v>
+      </c>
+      <c r="N45" t="s">
+        <v>352</v>
+      </c>
+      <c r="O45" t="s">
+        <v>412</v>
+      </c>
+      <c r="P45" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.003470044341342212</v>
+      </c>
+      <c r="D46">
+        <v>0.0001224246952915564</v>
+      </c>
+      <c r="E46">
+        <v>0.02159514836966991</v>
+      </c>
+      <c r="F46">
+        <v>0.002142298733815551</v>
+      </c>
+      <c r="G46">
+        <v>0.001743563450872898</v>
+      </c>
+      <c r="H46">
+        <v>1.000864748185982</v>
+      </c>
+      <c r="I46">
+        <v>0.04922087890773415</v>
+      </c>
+      <c r="J46">
+        <v>0.005669083446264267</v>
+      </c>
+      <c r="K46">
+        <v>0.4933910369873047</v>
+      </c>
+      <c r="L46">
+        <v>1.236027479171753</v>
+      </c>
+      <c r="M46">
+        <v>0.3244776427745819</v>
+      </c>
+      <c r="N46" t="s">
+        <v>353</v>
+      </c>
+      <c r="O46" t="s">
+        <v>413</v>
+      </c>
+      <c r="P46" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.006743760360511984</v>
+      </c>
+      <c r="D47">
+        <v>0.0002621597377583385</v>
+      </c>
+      <c r="E47">
+        <v>0.03480017185211182</v>
+      </c>
+      <c r="F47">
+        <v>0.002559027168899775</v>
+      </c>
+      <c r="G47">
+        <v>0.002056880621239543</v>
+      </c>
+      <c r="H47">
+        <v>1.000574009672607</v>
+      </c>
+      <c r="I47">
+        <v>0.04949834070868202</v>
+      </c>
+      <c r="J47">
+        <v>0.007533288560807705</v>
+      </c>
+      <c r="K47">
+        <v>1.360001087188721</v>
+      </c>
+      <c r="L47">
+        <v>1.991834878921509</v>
+      </c>
+      <c r="M47">
+        <v>0.431177943944931</v>
+      </c>
+      <c r="N47" t="s">
+        <v>354</v>
+      </c>
+      <c r="O47" t="s">
+        <v>414</v>
+      </c>
+      <c r="P47" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.01626006123826077</v>
+      </c>
+      <c r="D48">
+        <v>-0.0004092800954822451</v>
+      </c>
+      <c r="E48">
+        <v>0.09602063894271851</v>
+      </c>
+      <c r="F48">
+        <v>0.002423478756099939</v>
+      </c>
+      <c r="G48">
+        <v>0.002017860300838947</v>
+      </c>
+      <c r="H48">
+        <v>1.000269619175054</v>
+      </c>
+      <c r="I48">
+        <v>0.05139454090968276</v>
+      </c>
+      <c r="J48">
+        <v>-0.004262418020516634</v>
+      </c>
+      <c r="K48">
+        <v>-0.7384573817253113</v>
+      </c>
+      <c r="L48">
+        <v>5.495871067047119</v>
+      </c>
+      <c r="M48">
+        <v>-0.2439652532339096</v>
+      </c>
+      <c r="N48" t="s">
+        <v>355</v>
+      </c>
+      <c r="O48" t="s">
+        <v>415</v>
+      </c>
+      <c r="P48" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.03251296772942081</v>
+      </c>
+      <c r="D49">
+        <v>-0.00208706222474575</v>
+      </c>
+      <c r="E49">
+        <v>0.2150394171476364</v>
+      </c>
+      <c r="F49">
+        <v>0.002132556168362498</v>
+      </c>
+      <c r="G49">
+        <v>0.00185546837747097</v>
+      </c>
+      <c r="H49">
+        <v>0.9998653258508958</v>
+      </c>
+      <c r="I49">
+        <v>0.05357052117898859</v>
+      </c>
+      <c r="J49">
+        <v>-0.009705486707389355</v>
+      </c>
+      <c r="K49">
+        <v>-0.9989345073699951</v>
+      </c>
+      <c r="L49">
+        <v>12.30807113647461</v>
+      </c>
+      <c r="M49">
+        <v>-0.5555066466331482</v>
+      </c>
+      <c r="N49" t="s">
+        <v>356</v>
+      </c>
+      <c r="O49" t="s">
+        <v>416</v>
+      </c>
+      <c r="P49" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.08176060775681562</v>
+      </c>
+      <c r="D50">
+        <v>-0.006420589052140713</v>
+      </c>
+      <c r="E50">
+        <v>0.5495553612709045</v>
+      </c>
+      <c r="F50">
+        <v>0.001973687205463648</v>
+      </c>
+      <c r="G50">
+        <v>0.001978660468012094</v>
+      </c>
+      <c r="H50">
+        <v>1.000330614238203</v>
+      </c>
+      <c r="I50">
+        <v>0.059300464099035</v>
+      </c>
+      <c r="J50">
+        <v>-0.01168324332684278</v>
+      </c>
+      <c r="K50">
+        <v>-1</v>
+      </c>
+      <c r="L50">
+        <v>31.45454406738281</v>
+      </c>
+      <c r="M50">
+        <v>-0.6687062382698059</v>
+      </c>
+      <c r="N50" t="s">
+        <v>357</v>
+      </c>
+      <c r="O50" t="s">
+        <v>417</v>
+      </c>
+      <c r="P50" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.1508703387547918</v>
+      </c>
+      <c r="D51">
+        <v>-0.009806799702346325</v>
+      </c>
+      <c r="E51">
+        <v>1.022071480751038</v>
+      </c>
+      <c r="F51">
+        <v>0.002047127112746239</v>
+      </c>
+      <c r="G51">
+        <v>0.002616326790302992</v>
+      </c>
+      <c r="H51">
+        <v>1.001499388004896</v>
+      </c>
+      <c r="I51">
+        <v>0.0694370201069663</v>
+      </c>
+      <c r="J51">
+        <v>-0.009595023468136787</v>
+      </c>
+      <c r="K51">
+        <v>-1</v>
+      </c>
+      <c r="L51">
+        <v>58.49964141845703</v>
+      </c>
+      <c r="M51">
+        <v>-0.5491841435432434</v>
+      </c>
+      <c r="N51" t="s">
+        <v>358</v>
+      </c>
+      <c r="O51" t="s">
+        <v>418</v>
+      </c>
+      <c r="P51" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.00013204029175738</v>
+      </c>
+      <c r="D52">
+        <v>0.0002256535371998325</v>
+      </c>
+      <c r="E52">
+        <v>0.0007104335818439722</v>
+      </c>
+      <c r="F52">
+        <v>0.0009781306143850088</v>
+      </c>
+      <c r="G52">
+        <v>0.0009339269599877298</v>
+      </c>
+      <c r="H52">
+        <v>0.9996963501557294</v>
+      </c>
+      <c r="I52">
+        <v>0.04932442981861995</v>
+      </c>
+      <c r="J52">
+        <v>0.3176279067993164</v>
+      </c>
+      <c r="K52">
+        <v>1.094236850738525</v>
+      </c>
+      <c r="L52">
+        <v>0.04066262766718864</v>
+      </c>
+      <c r="M52">
+        <v>18.17986297607422</v>
+      </c>
+      <c r="N52" t="s">
+        <v>359</v>
+      </c>
+      <c r="O52" t="s">
+        <v>419</v>
+      </c>
+      <c r="P52" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0001656657572771539</v>
+      </c>
+      <c r="D53">
+        <v>0.0002779940550681204</v>
+      </c>
+      <c r="E53">
+        <v>0.0007517643389292061</v>
+      </c>
+      <c r="F53">
+        <v>0.00113291630987078</v>
+      </c>
+      <c r="G53">
+        <v>0.001095787156373262</v>
+      </c>
+      <c r="H53">
+        <v>0.9999900283785358</v>
+      </c>
+      <c r="I53">
+        <v>0.04930511052850404</v>
+      </c>
+      <c r="J53">
+        <v>0.3697888255119324</v>
+      </c>
+      <c r="K53">
+        <v>1.485785007476807</v>
+      </c>
+      <c r="L53">
+        <v>0.04302824661135674</v>
+      </c>
+      <c r="M53">
+        <v>21.16536331176758</v>
+      </c>
+      <c r="N53" t="s">
+        <v>360</v>
+      </c>
+      <c r="O53" t="s">
+        <v>420</v>
+      </c>
+      <c r="P53" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.000195807509436986</v>
+      </c>
+      <c r="D54">
+        <v>0.0003189416602253914</v>
+      </c>
+      <c r="E54">
+        <v>0.0007834442658349872</v>
+      </c>
+      <c r="F54">
+        <v>0.001285409554839134</v>
+      </c>
+      <c r="G54">
+        <v>0.001216954435221851</v>
+      </c>
+      <c r="H54">
+        <v>1.000264607398514</v>
+      </c>
+      <c r="I54">
+        <v>0.04924341025777244</v>
+      </c>
+      <c r="J54">
+        <v>0.4071018993854523</v>
+      </c>
+      <c r="K54">
+        <v>1.841977834701538</v>
+      </c>
+      <c r="L54">
+        <v>0.04484149068593979</v>
+      </c>
+      <c r="M54">
+        <v>23.30102729797363</v>
+      </c>
+      <c r="N54" t="s">
+        <v>361</v>
+      </c>
+      <c r="O54" t="s">
+        <v>421</v>
+      </c>
+      <c r="P54" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.0003078925217778459</v>
+      </c>
+      <c r="D55">
+        <v>0.0004564720438793302</v>
+      </c>
+      <c r="E55">
+        <v>0.0009189807460643351</v>
+      </c>
+      <c r="F55">
+        <v>0.001737853395752609</v>
+      </c>
+      <c r="G55">
+        <v>0.001535052084363997</v>
+      </c>
+      <c r="H55">
+        <v>1.000605432023086</v>
+      </c>
+      <c r="I55">
+        <v>0.04919533700523394</v>
+      </c>
+      <c r="J55">
+        <v>0.4967155754566193</v>
+      </c>
+      <c r="K55">
+        <v>3.459322452545166</v>
+      </c>
+      <c r="L55">
+        <v>0.05259910598397255</v>
+      </c>
+      <c r="M55">
+        <v>28.4301872253418</v>
+      </c>
+      <c r="N55" t="s">
+        <v>362</v>
+      </c>
+      <c r="O55" t="s">
+        <v>422</v>
+      </c>
+      <c r="P55" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0004325459656228813</v>
+      </c>
+      <c r="D56">
+        <v>0.0005873829941265285</v>
+      </c>
+      <c r="E56">
+        <v>0.001136424019932747</v>
+      </c>
+      <c r="F56">
+        <v>0.002387929707765579</v>
+      </c>
+      <c r="G56">
+        <v>0.001956693362444639</v>
+      </c>
+      <c r="H56">
+        <v>1.000534509234188</v>
+      </c>
+      <c r="I56">
+        <v>0.04961936787837967</v>
+      </c>
+      <c r="J56">
+        <v>0.5168695449829102</v>
+      </c>
+      <c r="K56">
+        <v>5.84538459777832</v>
+      </c>
+      <c r="L56">
+        <v>0.06504476070404053</v>
+      </c>
+      <c r="M56">
+        <v>29.58372688293457</v>
+      </c>
+      <c r="N56" t="s">
+        <v>363</v>
+      </c>
+      <c r="O56" t="s">
+        <v>423</v>
+      </c>
+      <c r="P56" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0005623776180196308</v>
+      </c>
+      <c r="D57">
+        <v>0.0007309295469895005</v>
+      </c>
+      <c r="E57">
+        <v>0.001517999335192144</v>
+      </c>
+      <c r="F57">
+        <v>0.002586626447737217</v>
+      </c>
+      <c r="G57">
+        <v>0.002098870929330587</v>
+      </c>
+      <c r="H57">
+        <v>1.000147059109571</v>
+      </c>
+      <c r="I57">
+        <v>0.05001899306633641</v>
+      </c>
+      <c r="J57">
+        <v>0.4815084636211395</v>
+      </c>
+      <c r="K57">
+        <v>9.951349258422852</v>
+      </c>
+      <c r="L57">
+        <v>0.0868847444653511</v>
+      </c>
+      <c r="M57">
+        <v>27.55978775024414</v>
+      </c>
+      <c r="N57" t="s">
+        <v>364</v>
+      </c>
+      <c r="O57" t="s">
+        <v>424</v>
+      </c>
+      <c r="P57" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.0007563694545691774</v>
+      </c>
+      <c r="D58">
+        <v>0.000885777291841805</v>
+      </c>
+      <c r="E58">
+        <v>0.002434637630358338</v>
+      </c>
+      <c r="F58">
+        <v>0.002206422621384263</v>
+      </c>
+      <c r="G58">
+        <v>0.001965002156794071</v>
+      </c>
+      <c r="H58">
+        <v>0.9996358390055878</v>
+      </c>
+      <c r="I58">
+        <v>0.05278989786629319</v>
+      </c>
+      <c r="J58">
+        <v>0.3638230562210083</v>
+      </c>
+      <c r="K58">
+        <v>17.18052291870117</v>
+      </c>
+      <c r="L58">
+        <v>0.1393497735261917</v>
+      </c>
+      <c r="M58">
+        <v>20.82390403747559</v>
+      </c>
+      <c r="N58" t="s">
+        <v>365</v>
+      </c>
+      <c r="O58" t="s">
+        <v>425</v>
+      </c>
+      <c r="P58" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.000914111970066425</v>
+      </c>
+      <c r="D59">
+        <v>0.0010209841420874</v>
+      </c>
+      <c r="E59">
+        <v>0.0035664695315063</v>
+      </c>
+      <c r="F59">
+        <v>0.001962414942681789</v>
+      </c>
+      <c r="G59">
+        <v>0.001814117887988687</v>
+      </c>
+      <c r="H59">
+        <v>0.999101079936571</v>
+      </c>
+      <c r="I59">
+        <v>0.05550104495513812</v>
+      </c>
+      <c r="J59">
+        <v>0.2862730622291565</v>
+      </c>
+      <c r="K59">
+        <v>27.30900192260742</v>
+      </c>
+      <c r="L59">
+        <v>0.2041317075490952</v>
+      </c>
+      <c r="M59">
+        <v>16.38522529602051</v>
+      </c>
+      <c r="N59" t="s">
+        <v>366</v>
+      </c>
+      <c r="O59" t="s">
+        <v>426</v>
+      </c>
+      <c r="P59" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.001119885517382384</v>
+      </c>
+      <c r="D60">
+        <v>0.001109814853407443</v>
+      </c>
+      <c r="E60">
+        <v>0.005829226225614548</v>
+      </c>
+      <c r="F60">
+        <v>0.001947057317011058</v>
+      </c>
+      <c r="G60">
+        <v>0.002081835875287652</v>
+      </c>
+      <c r="H60">
+        <v>0.9995843202085551</v>
+      </c>
+      <c r="I60">
+        <v>0.06107209231604536</v>
+      </c>
+      <c r="J60">
+        <v>0.190388023853302</v>
+      </c>
+      <c r="K60">
+        <v>36.85695648193359</v>
+      </c>
+      <c r="L60">
+        <v>0.3336436450481415</v>
+      </c>
+      <c r="M60">
+        <v>10.89711570739746</v>
+      </c>
+      <c r="N60" t="s">
+        <v>367</v>
+      </c>
+      <c r="O60" t="s">
+        <v>427</v>
+      </c>
+      <c r="P60" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.00126370306824908</v>
+      </c>
+      <c r="D61">
+        <v>0.001184470136649907</v>
+      </c>
+      <c r="E61">
+        <v>0.007558605633676052</v>
+      </c>
+      <c r="F61">
+        <v>0.002059648046270013</v>
+      </c>
+      <c r="G61">
+        <v>0.002770863706246018</v>
+      </c>
+      <c r="H61">
+        <v>1.001223990208078</v>
+      </c>
+      <c r="I61">
+        <v>0.07011747465255234</v>
+      </c>
+      <c r="J61">
+        <v>0.156704843044281</v>
+      </c>
+      <c r="K61">
+        <v>47.32776260375977</v>
+      </c>
+      <c r="L61">
+        <v>0.4326269924640656</v>
+      </c>
+      <c r="M61">
+        <v>8.969213485717773</v>
+      </c>
+      <c r="N61" t="s">
+        <v>368</v>
+      </c>
+      <c r="O61" t="s">
+        <v>428</v>
+      </c>
+      <c r="P61" t="s">
+        <v>488</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/rf_standard_l2/performance.xlsx
+++ b/scripts/rf_standard_l2/performance.xlsx
@@ -9108,12 +9108,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0006457233685068786</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.0002076855162158608</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.00048778613563627</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.0006827405886724591</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.0007426517549902201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.0004845221701543778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0002992365625686944</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0003961616603191942</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0009724429110065103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0004175179346930236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.0004306811315473169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>-8.319482731167227E-05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.002487251069396734</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>-0.000155509143951349</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0001992941251955926</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.0002109640627168119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.0002054003125522286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.001036982168443501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>8.231361425714567E-05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0005022578407078981</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.0002233170816907659</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.001075867447070777</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.001064932905137539</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.001128165167756379</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.0009563898202031851</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.0002610018127597868</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>-5.479096216731705E-05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-0.0003643249801825732</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>-0.0008216488640755415</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>-0.0002061671548290178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.0004171582986600697</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>6.051688978914171E-05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.0001062373485183343</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0002524338196963072</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.0005801113438792527</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>-0.0001552525645820424</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.0005384316900745034</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.0005883079138584435</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.001641653245314956</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0004198050883132964</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>2.046150621026754E-05</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.001428851974196732</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>-4.482673102756962E-05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>-0.0001306052872678265</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.001555042341351509</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.0002585261827334762</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.0001310419029323384</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.0002499525144230574</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0003322584379930049</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.0006282319664023817</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>-0.0004948024288751185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>-0.0001739048166200519</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>2.144043719454203E-05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.0004011874552816153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.0002627428912092</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.0005780957289971411</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.0007125990814529359</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.0001859470212366432</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.0009192369179800153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.0005150427459739149</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.0003460612497292459</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.0003442141169216484</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.0007277275435626507</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.001874751062132418</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0003477598074823618</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.0003215073375031352</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.0004318587598390877</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.0003925703931599855</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.001046085613779724</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.000400541175622493</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>0.0004877870669588447</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.0002760293136816472</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>0.0003917539725080132</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.001141381915658712</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.001180191757157445</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-0.0008364950190298259</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.002693201648071408</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>0.0002475623623467982</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>0.0003076764987781644</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>-7.89157347753644E-05</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>3.289620144641958E-05</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.0001685860188445076</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>0.0005470073083415627</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>0.0004104122053831816</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>0.0002079523692373186</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>0.0004114467010367662</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.0005648124497383833</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>0.0002971411449834704</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.0007798679871484637</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0005352461594156921</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>0.0004834622086491436</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>0.001415782608091831</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0005103349685668945</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.00154355017002672</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>5.251163020147942E-05</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0004033785371575505</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.0003858950221911073</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.0005481427651830018</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>0.0002245347131974995</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>-3.44115833286196E-05</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>0.0005094744847156107</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-0.0001470097340643406</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>0.002003262750804424</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.0003256930795032531</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0003146618255414069</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.001131084049120545</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.001289754407480359</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>0.0003095340507570654</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>0.0004025153175462037</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.001585130346938968</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>0.0002059835533145815</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>1.754611730575562E-05</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>0.0004626668815035373</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-0.0002005542337428778</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>0.0002336231264052913</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>0.0004602679691743106</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>-0.000261647772276774</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>0.000177667592652142</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>0.0002819306391756982</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>5.02656439493876E-05</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.0008297963067889214</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>0.0002240568428533152</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.0004791290266439319</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.0003147856041323394</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>0.0002549912314862013</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.000852345023304224</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>0.0008231421816162765</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>0.0008545878226868808</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>3.027714774361812E-05</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>0.001592800719663501</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>0.0003043877659365535</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>-5.552195216296241E-05</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>-1.096599135053111E-05</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>0.0005556646501645446</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0004697357071563601</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.001216496573761106</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.0001997502549784258</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>5.004488048143685E-05</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.0009438820998184383</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>2.082046012219507E-05</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0006213996675796807</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.004280004184693098</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>0.0009257092606276274</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.0008660540916025639</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0.001119582797400653</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>0.0002972878573928028</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.001327713136561215</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.0007558923098258674</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.0007107561687007546</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.000237839893088676</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>0.000357572571374476</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.0009495095000602305</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>0.0002836647909134626</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>5.90009985899087E-05</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.004223710391670465</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>0.0009267026325687766</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>0.0005128856864757836</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.00129375874530524</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0006291685858741403</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>0.0004721422446891665</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0004541392554529011</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.0008448283770121634</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.0007115964544937015</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.000898839789442718</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>0.0005898879026062787</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.0009189285920001566</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>0.0001680325076449662</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.002192095853388309</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.0008993782685138285</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>-2.274705730087589E-05</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>5.989866986055858E-05</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>0.0005206005880609155</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>-0.0004417585150804371</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>1.348445312032709E-05</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0003508259833324701</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.000768406200222671</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>0.0004530542646534741</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.000486700504552573</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.0005979093257337809</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0006045582122169435</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>-0.001178031205199659</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>-0.0004875785962212831</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>-2.596794001874514E-05</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>0.0006876451661810279</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>0.0007016778690740466</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>0.0003255364717915654</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.001206710003316402</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.0007506730034947395</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.0002115205570589751</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.0002768900303635746</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.001153849298134446</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>0.0001446290116291493</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>-0.001372768194414675</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>-0.003723598551005125</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>0.002038284437730908</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>0.0002521199057810009</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0006079542217776179</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>0.0004341552848927677</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>0.0001078509958460927</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.000474552798550576</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>5.954335938440636E-05</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>0.0002256939915241674</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.0006499248556792736</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0006054497207514942</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>6.981348997214809E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0002945270971395075</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.003177176462486386</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>-0.0006969211390241981</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.0001022831274894997</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>4.635060031432658E-05</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>0.0007432432030327618</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.0001943116076290607</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>0.00050239177653566</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>0.0003959965542890131</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>0.0003496620920486748</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0005627276841551065</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0003938238951377571</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>-0.0001142095061368309</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.000576645543333143</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.002680882345885038</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.0005621167365461588</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>-0.0002318679762538522</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.001152343233115971</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.0003303389239590615</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.0005644272896461189</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>0.0009349008905701339</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>-3.169770570821129E-05</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.0007519657956436276</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.0004289774515200406</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.000381887482944876</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0001943526440300047</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>-0.00061194715090096</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.000250202720053494</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.0007437522290274501</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>8.354979945579544E-05</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.0005668645026162267</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>0.001055491389706731</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>0.0005517308600246906</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>-0.0002432014152873307</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.001033549662679434</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>0.0001110641751438379</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>5.07784316141624E-05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0004700737481471151</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>0.0001684100134298205</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>0.0005074837827123702</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.003046713536605239</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0004196198133286089</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>-0.0001240882120328024</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0001933150342665613</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>0.0001600936229806393</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0003830204368568957</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0006623720983043313</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>0.0001420654734829441</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>9.493932884652168E-05</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>0.000313824915792793</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>0.0001791407994460315</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.0004589864693116397</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>0.0002073754731100053</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001624825061298907</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>-0.0003619705094024539</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.0006005513132549822</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>0.0003061300085391849</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>7.899756019469351E-05</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>0.000387940468499437</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0007333127432502806</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>0.0005010751774534583</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>0.0004120730154681951</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>0.0008842454990372062</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>0.000213548744795844</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0005750037962570786</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.0007438637549057603</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.002550818491727114</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>0.0006847225013189018</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>0.0004659648984670639</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>0.000481047376524657</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>0.0005810139700770378</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>0.0002878378727473319</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.0005043543060310185</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>0.0001076946136890911</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0005176545237191021</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.0002013984631048515</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0003067818179260939</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>0.0001642259157961234</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>-0.0004812729603145272</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>0.00136976083740592</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.0005909368628636003</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.000831548182759434</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.000346504501067102</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>9.411389328306541E-05</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>1.133915338868974E-05</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.001047452096827328</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.0002133400121238083</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>5.648697697324678E-05</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.0006813918007537723</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.0002679000899661332</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0001505611871834844</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0001757885620463639</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.001845931634306908</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>-7.742371235508472E-05</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.0006690230220556259</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>0.0001382074115099385</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.0001895364403026178</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.000394909642636776</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>0.0006434820243157446</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.0002899631799664348</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0002808735298458487</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-0.0003951634280383587</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.0005077689420431852</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>0.0003097130393143743</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>-0.0001268014748347923</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>0.0001088619756046683</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>-7.607994484715164E-05</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.001217289944179356</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.0005787237314507365</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.0004024415684398264</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.0003722822002600878</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>0.001235500094480813</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>-0.0003419044078327715</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>0.0003139674372505397</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.0009396963869221509</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.0003199535713065416</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>-4.450602500583045E-05</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0005558689590543509</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.001450575538910925</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>-0.0002442231343593448</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.0008138536941260099</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>0.000517524138558656</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>0.000440270930994302</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>0.0001304005418205634</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>0.0003137755556963384</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.001063625328242779</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.000873063167091459</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.0007410311372950673</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.0007769752410240471</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.000448136095656082</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.00175277388188988</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.001383099122904241</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>0.0002608034119475633</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>0.0009684543474577367</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>-0.0003952310071326792</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>0.0009929001098498702</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>0.000667020445689559</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>0.000359182246029377</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.001108417753130198</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>0.0001751181407598779</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.0003582184435799718</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.0003221054212190211</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0003581236524041742</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.0008622290915809572</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.0006167262909002602</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.001130095799453557</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.0004452885768841952</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0004184178833384067</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.0004222205898258835</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.000330343667883426</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.001011815737001598</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>0.0001224455627379939</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>0.0001100511144613847</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0005977987311780453</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>-0.0002161406591767445</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>0.0001136082137236372</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.002492396393790841</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-0.0002298966574016958</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.001187619171105325</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>0.0005259437020868063</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.0009099322487600148</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>0.0001429628464393318</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.0009618439362384379</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>-3.02007065329235E-05</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>6.342318374663591E-05</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>0.0006066688802093267</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0004924259264953434</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.0006074385601095855</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>0.0001270313659915701</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.00136189186014235</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.00339565216563642</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>1.870542109827511E-05</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>2.583463901828509E-05</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>0.0004780993913300335</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>0.000326765701174736</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.0008227344951592386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>-2.746231302808155E-06</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0003670964215416461</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>0.0004910212592221797</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>0.0005235221469774842</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.001093691098503768</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.001043326919898391</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001126278773881495</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.0005673974519595504</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>0.0009951478568837047</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.000266838411334902</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.001260614488273859</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.001077153487131</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.0002579599095042795</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>0.0004145863349549472</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>0.000161942676641047</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0001504210667917505</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>0.0002031809708569199</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>-0.0001010491760098375</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>0.0004421557823661715</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>-0.0003412287624087185</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>0.0005404165131039917</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.001014709938317537</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.0009309577289968729</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-0.0003216390323359519</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.001737423473969102</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>0.001018352573737502</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-7.429598917951807E-05</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>0.0004669461923185736</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>8.081228588707745E-05</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>0.001671277335844934</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>0.0004287904885131866</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>0.0002224071649834514</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>-0.0008743093349039555</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>0.0005173644749447703</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.0004143501573707908</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>0.0006400261772796512</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.0007152066100388765</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.0004575093335006386</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0002436026697978377</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.001091218553483486</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>-7.165202987380326E-05</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.0007934989407658577</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.0001767037028912455</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.001319442759267986</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.000421241536969319</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.001559294178150594</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>0.001373926177620888</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.0005720632616430521</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>0.0001874525041785091</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0005467638839036226</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0003489520458970219</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.0004565285635180771</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.000493004044983536</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0003867993946187198</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.0008834665059112012</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.001739877508953214</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>-5.783593951491639E-05</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.001787806628271937</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.00348474713973701</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>0.0004304369213059545</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.0007289867498911917</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0005078538088127971</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.0005615855916403234</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>8.665735367685556E-05</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0004117254284210503</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.000320230086799711</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>0.0002843787078745663</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>0.0005859772791154683</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>-0.0004984919214621186</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>-0.0001415481092408299</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>8.504092693328857E-05</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001392095698975027</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.0005210885428823531</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.0007812926196493208</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0004919411148875952</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0007357096765190363</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0006997755263000727</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>0.0002072669012704864</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.001036514644511044</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.0004046447284054011</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.001685078721493483</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.0002385408442933112</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.0002803693350870162</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.0005581905134022236</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0004515110922511667</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001174469594843686</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0005819944199174643</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001351208775304258</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.0004706627514678985</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>0.0004478852497413754</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>0.0001270244538318366</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.0001783380575943738</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.0002778743219096214</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>0.0003391880600247532</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>0.0003299218369647861</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>0.001039676484651864</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.001021228148601949</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.00606409041211009</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.0006635676836594939</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>9.300816600443795E-05</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.000609956041444093</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>0.0004020406922791153</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.0005477849626913667</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-8.883658608738187E-08</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0003807151806540787</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>0.000219919573282823</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.0009375335648655891</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.0002499210240785033</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>0.0005311276763677597</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0003912595275323838</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.001402299851179123</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0006383720319718122</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0005522593855857849</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>0.0005204754415899515</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.0006590828998014331</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>0.0002939391997642815</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0001415888691553846</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>0.0004656962119042873</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.0004225936718285084</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.000396922550862655</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.0005972288199700415</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001220283447764814</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>0.001350937876850367</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>-0.0009906315244734287</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.001510999747551978</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.0007743347086943686</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>0.0003542175109032542</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.0007232410134747624</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>-1.411744142387761E-05</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.0003863182209897786</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0005166762857697904</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.0001703760935924947</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>9.497735845798161E-06</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>-8.076822996372357E-05</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>8.408522262470797E-05</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.0008420575759373605</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.000476584886200726</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>0.0006940473685972393</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>0.0001487098488723859</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0006112102419137955</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.0004770310479216278</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.0009156772284768522</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001397871412336826</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>0.00164421065710485</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.0008973232470452785</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>8.024383714655414E-05</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>0.0002022090484388173</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.0004433547437656671</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.0003845900355372578</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0005382468807511032</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>0.0002329923881916329</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.0006578723550774157</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.0006169442203827202</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>0.0001310703955823556</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.001084939343854785</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>0.0008737540920265019</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.003637799527496099</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>0.0001623602292966098</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>0.0004200000839773566</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0005649934173561633</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.0001769222726579756</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>0.0008137205732055008</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>0.0001222095015691593</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.000700406963005662</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>0.0004842850030399859</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.0008520288392901421</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.000434981076978147</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>0.0005420589586719871</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.0005522533901967108</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001530588138848543</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.001272149034775794</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.0003620196657720953</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0006974266143515706</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.000653423776384443</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.0004843947244808078</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>0.0009276369819417596</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.0007835484575480223</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>0.001034067594446242</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>-7.483950321329758E-05</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>8.550610800739378E-05</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>0.0001885715173557401</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>0.0004745678743347526</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>0.002881371416151524</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.0004095872864127159</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0001869442203314975</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.0002983652811963111</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>0.0003446084447205067</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>2.718908717724844E-06</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>0.0005911075277253985</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.0004633609496522695</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.0006877504056319594</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.0007353367400355637</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.000344844360370189</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>0.0003841675934381783</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>0.0008047035662457347</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>0.001244411338120699</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>0.0004391338443383574</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>0.0003567075473256409</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.0009955192217603326</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001258587348274887</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>0.0003869796055369079</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.0002592657401692122</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0002253191923955455</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.000373904564185068</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>0.0001646107266424224</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-2.215802669525146E-05</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.0002841724781319499</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>0.0002195710112573579</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>0.002295184647664428</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.0002876287326216698</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.000377991673303768</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>0.0003902642638422549</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0005580694996751845</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0004591255565173924</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.0004886898677796125</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>0.0004891155986115336</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>-7.908324914751574E-05</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>0.0005113760707899928</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.001229032641276717</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.0009189105476252735</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.00171691772993654</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.008045854046940804</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.0005699084722436965</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>-0.0001564045232953504</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.001041264273226261</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.001404035603627563</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.0002421868994133547</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0002102887665387243</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.0003059894952457398</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>9.326521831098944E-05</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.0005875902716070414</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>0.000146526173921302</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.0007655704393982887</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>0.0006579423788934946</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>-0.000578586186747998</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.0008861623355187476</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>-0.0001771887909853831</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0003052342508453876</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.0009570129914209247</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>-0.001083807903341949</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.0007599937962368131</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>0.0007218660321086645</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>0.0007709258934482932</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>0.0004538432112894952</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.0003752078046090901</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.0003687020798679441</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>0.0005097473622299731</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>-0.004237041808664799</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0004182904376648366</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001012832275591791</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>0.0003961268230341375</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.0009849638445302844</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.000249342032475397</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>0.0004505513061303645</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0004543194372672588</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.0005129978526383638</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0004316139093134552</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.0007738681160844862</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>0.0005443589179776609</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>0.0004026310925837606</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>-0.002407421125099063</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.0003358743852004409</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.001838748692534864</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0006997949094511569</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>0.0001373620616504923</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>-0.001217658165842295</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>-0.0005878107622265816</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.0007624432910233736</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>6.336147180263652E-06</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>-4.109716974198818E-05</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.0003291377797722816</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>-0.002480992814525962</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>0.00132478482555598</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.0007660488481633365</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>0.0007767961942590773</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.000211033271625638</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>0.0005125554162077606</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>-0.0007212354685179889</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.003247747430577874</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.0008487229933962226</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>-0.0002500979753676802</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.0007495965110138059</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.001139024505391717</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.0004558569635264575</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>0.0005622176104225218</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.001660057110711932</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.00522399740293622</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.0006740992539562285</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.000278646475635469</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>0.0003017048293258995</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>-0.0002894483041018248</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0003496023709885776</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>0.0005138198612257838</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>-5.116545071359724E-05</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.0007723082671873271</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>0.0002654435229487717</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0004276692925486714</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>2.02120154426666E-05</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>0.0002770212304312736</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.006497135385870934</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>8.557148248655722E-05</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.0005956876557320356</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>0.0001495299366069958</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.0005000811070203781</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.0005125210736878216</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>0.000244150374783203</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.0002797860652208328</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>0.0003139945911243558</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.0009363519493490458</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>0.0003097170265391469</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>0.0001566384889883921</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.001172355143353343</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.001525832689367235</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>4.660174454329535E-06</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>-0.0001506280095782131</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.0006780021940357983</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>0.0008499420364387333</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>0.0005634636618196964</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>-8.756006718613207E-05</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>0.0001853892317740247</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.000869955460075289</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>0.000368787586921826</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0004095561744179577</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.0001185468136100098</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>0.0002309924457222223</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>-0.008042388595640659</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>0.0001738805294735357</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.0008651104872114956</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>0.0001630815968383104</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>1.249631986866007E-05</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>0.0001964906550711021</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>0.0001403015048708767</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>0.0001178432139568031</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>0.0002708103565964848</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>0.0007835565484128892</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0003385020536370575</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>-7.126103446353227E-05</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>0.0009636938339099288</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>0.007414539344608784</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>-2.454330206091981E-05</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>0.0002314214943908155</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>7.439202454406768E-05</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>-3.439789361436851E-05</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>0.0003412962832953781</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.0003885880869347602</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.0003249316068831831</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.0002926115412265062</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>0.000132200846564956</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>-0.000126557657495141</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0002230601094197482</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>0.0009027728228829801</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.005021750926971436</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.0002533899678383023</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.000294811965432018</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0001800317404558882</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>0.000387184030842036</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0003092967090196908</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>-6.460298754973337E-05</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>5.573636371991597E-05</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>8.988857007352635E-05</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.0003240933001507074</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>-2.354023854422849E-05</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.0008279206231236458</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>1.053951746143866E-05</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>0.001308125909417868</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.001877572271041572</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.0009956957073882222</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.0003377468965481967</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>3.09889655909501E-05</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>0.0002466590667609125</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0001630585320526734</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.0003357607638463378</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.0002810643054544926</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0004812522092834115</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0003002653538715094</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.0002191804378526285</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.0002717121096793562</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.003283163765445352</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.0002799216599669307</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>-1.917083682201337E-05</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>2.392556416452862E-05</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0001796334836399183</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>9.352261258754879E-05</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.0003157224564347416</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.0004182569973636419</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.0002887198061216623</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>0.0001733458775561303</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0002464573772158474</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0005011423490941525</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>0.0001771727547748014</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>0.0004971545422449708</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.0005308165564201772</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001119092339649796</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>-0.0002540428249631077</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-8.323261135956272E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.0002482577692717314</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>4.439194526639767E-05</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.002088651992380619</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.000352524482877925</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>0.0005077804671600461</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.0004827987868338823</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>-1.080753554560943E-05</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>0.0003240520018152893</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>0.0003275363415013999</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.0001756261626724154</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0003404481685720384</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>3.957617445848882E-05</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>0.0001372410479234532</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.0004550279991235584</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.0002681329206097871</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.004091955255717039</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>-0.0002945462183561176</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0002749377454165369</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>4.99462075822521E-05</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>-1.831138433772139E-05</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>0.0001872412394732237</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>0.0001852309214882553</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>0.0003337898815516382</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0004556647327262908</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>9.637949551688507E-05</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-4.750921107188333E-06</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>8.154728129738942E-05</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>0.0006458166753873229</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>0.000166505400557071</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>1.081226309906924E-05</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>2.200036760768853E-05</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.0006688409484922886</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0002331498544663191</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>0.0004354144912213087</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.0004958720528520644</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0004104613035451621</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0002050091425189748</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.0003688315628096461</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.0002450500323902816</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0004247478791512549</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>-0.0003504867490846664</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.0003671069862321019</v>
       </c>
     </row>
   </sheetData>
@@ -9123,12 +15667,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.008199572563171387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.006811261177062988</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.001404643058776855</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.004186153411865234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.007259488105773926</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.007644414901733398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.004677295684814453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.007766366004943848</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.005965113639831543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.006785750389099121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.008301496505737305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.012176513671875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.01063632965087891</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.001724600791931152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.002365469932556152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-9.85264778137207E-05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.001631021499633789</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.004867434501647949</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.007846236228942871</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.00393974781036377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.00720524787902832</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.005108356475830078</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.001951813697814941</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.002937436103820801</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.002743005752563477</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.009555816650390625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.007548332214355469</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.00443577766418457</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.00921785831451416</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.007885932922363281</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.005359530448913574</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.006233334541320801</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.008480429649353027</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.01147198677062988</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.001070141792297363</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.008013367652893066</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.01245975494384766</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.006884217262268066</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.007386207580566406</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.004318594932556152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.008514642715454102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.009828567504882812</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.01017343997955322</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.006179928779602051</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.007836222648620605</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.005927324295043945</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.01622641086578369</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.00472724437713623</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.001940727233886719</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.001714944839477539</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.003736972808837891</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.001126766204833984</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.008996129035949707</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.007035255432128906</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>-0.00499492883682251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.01105546951293945</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.007675290107727051</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.006734490394592285</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>-0.000435948371887207</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.005654215812683105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.006859302520751953</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.00246727466583252</v>
       </c>
     </row>
   </sheetData>
@@ -9138,12 +16178,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.02815830707550049</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.03327023983001709</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.03565788269042969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.01830005645751953</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.0200965404510498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.03923749923706055</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0330129861831665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.03965950012207031</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.04325687885284424</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.03083992004394531</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.01594114303588867</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.03102719783782959</v>
       </c>
     </row>
   </sheetData>
